--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$108</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$118</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$95</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4309,7 +4309,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 2.5, "op_wape_pct": 86.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 1092.86, "rev_act": 1098.95, "op_pred": -9.26, "op_act": -69.66}, {"q": "2025Q4", "rev_pred": 1004.22, "rev_act": 963.22, "op_pred": -8.51, "op_act": -22.38}, {"q": "2026Q1", "rev_pred": 1019.23, "rev_act": 964.25, "op_pred": -8.63, "op_act": -14.39}, {"q": "2026Q2", "rev_pred": 1067.88, "rev_act": 1067.67, "op_pred": -9.05, "op_act": 21.74}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 2.5, "op_wape_pct": 86.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 1092.86, "rev_act": 1098.95, "op_pred": -9.26, "op_act": -69.66}, {"q": "2025Q4", "rev_pred": 1004.22, "rev_act": 963.22, "op_pred": -8.51, "op_act": -22.38}, {"q": "2026Q1", "rev_pred": 1019.23, "rev_act": 964.25, "op_pred": -8.63, "op_act": -14.39}, {"q": "2026Q2", "rev_pred": 1067.88, "rev_act": 1067.67, "op_pred": -9.05, "op_act": 21.74}]}</t>
         </is>
       </c>
     </row>
@@ -10136,7 +10136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO108"/>
+  <dimension ref="A1:AO118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12594,10 +12594,10 @@
         <v>115935.86</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>107219.3</v>
+        <v>96735.11</v>
       </c>
       <c r="Z25" s="34" t="n">
-        <v>107219.3</v>
+        <v>96735.11</v>
       </c>
       <c r="AA25" s="18" t="n">
         <v>106190</v>
@@ -12682,7 +12682,12 @@
       <c r="V26" s="18" t="n">
         <v>572.6</v>
       </c>
-      <c r="Z26" s="9" t="n"/>
+      <c r="Y26" s="18" t="n">
+        <v>10484.18</v>
+      </c>
+      <c r="Z26" s="34" t="n">
+        <v>10484.18</v>
+      </c>
       <c r="AB26" s="5" t="n"/>
       <c r="AC26" s="10" t="n"/>
       <c r="AD26" s="10" t="n"/>
@@ -15044,10 +15049,10 @@
         <v>126430.59</v>
       </c>
       <c r="Y52" s="18" t="n">
-        <v>135856.68</v>
+        <v>135856.67</v>
       </c>
       <c r="Z52" s="34" t="n">
-        <v>135856.68</v>
+        <v>135856.67</v>
       </c>
       <c r="AA52" s="18" t="n">
         <v>117943.07</v>
@@ -15139,10 +15144,10 @@
         <v>115231.26</v>
       </c>
       <c r="Y53" s="18" t="n">
-        <v>124875.38</v>
+        <v>124875.37</v>
       </c>
       <c r="Z53" s="34" t="n">
-        <v>124875.38</v>
+        <v>124875.37</v>
       </c>
       <c r="AA53" s="18" t="n">
         <v>109492.52</v>
@@ -15565,12 +15570,7 @@
       <c r="U59" s="34" t="n">
         <v>143242.68</v>
       </c>
-      <c r="Y59" s="18" t="n">
-        <v>107219.3</v>
-      </c>
-      <c r="Z59" s="34" t="n">
-        <v>107219.3</v>
-      </c>
+      <c r="Z59" s="9" t="n"/>
       <c r="AB59" s="19" t="n">
         <v>97273.92999999999</v>
       </c>
@@ -17730,78 +17730,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>-2675.54</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>-1261.68</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>-12165.09</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>2442.21</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>8126.82</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>-2857.74</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>-6154.45</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>20108.73</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>4404.98</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>6219.3</v>
-      </c>
-      <c r="P86" s="34" t="n">
-        <v>24578.56</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>-5958.74</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>12271.57</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>-19295.86</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>32937.13</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>19954.1</v>
-      </c>
-      <c r="V86" s="18" t="n">
-        <v>3827.83</v>
-      </c>
-      <c r="W86" s="18" t="n">
-        <v>37329.48</v>
-      </c>
-      <c r="X86" s="18" t="n">
-        <v>-34.48</v>
-      </c>
-      <c r="Y86" s="18" t="n">
-        <v>301.28</v>
-      </c>
-      <c r="Z86" s="34" t="n">
-        <v>41424.11</v>
-      </c>
-      <c r="AA86" s="18" t="n">
-        <v>-12125.26</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
+      <c r="Z86" s="9" t="n"/>
       <c r="AB86" s="19" t="n">
-        <v>12030.08</v>
+        <v>128.09</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17823,78 +17761,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>58.61</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>-40.6</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>32.55</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>285.84</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>52.66</v>
-      </c>
-      <c r="U87" s="34" t="n">
-        <v>202.51</v>
-      </c>
-      <c r="V87" s="18" t="n">
-        <v>177.65</v>
-      </c>
-      <c r="W87" s="18" t="n">
-        <v>173.26</v>
-      </c>
-      <c r="X87" s="18" t="n">
-        <v>207.26</v>
-      </c>
-      <c r="Y87" s="18" t="n">
-        <v>492.63</v>
-      </c>
-      <c r="Z87" s="34" t="n">
-        <v>1050.8</v>
-      </c>
-      <c r="AA87" s="18" t="n">
-        <v>146.78</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
+      <c r="Z87" s="9" t="n"/>
       <c r="AB87" s="19" t="n">
-        <v>127.91</v>
+        <v>0</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -17916,70 +17792,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>-1357.25</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="G88" s="18" t="n">
-        <v>-1437.3</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>-1718.35</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>-2036.47</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>-2608.64</v>
-      </c>
-      <c r="K88" s="34" t="n">
-        <v>-7800.76</v>
-      </c>
-      <c r="L88" s="18" t="n">
-        <v>-2635.89</v>
-      </c>
-      <c r="M88" s="18" t="n">
-        <v>-2892.55</v>
-      </c>
+      <c r="K88" s="9" t="n"/>
       <c r="P88" s="9" t="n"/>
-      <c r="Q88" s="18" t="n">
-        <v>-2821.94</v>
-      </c>
-      <c r="R88" s="18" t="n">
-        <v>-2758.24</v>
-      </c>
-      <c r="S88" s="18" t="n">
-        <v>-2723.2</v>
-      </c>
-      <c r="T88" s="18" t="n">
-        <v>-2348.38</v>
-      </c>
-      <c r="U88" s="34" t="n">
-        <v>-10651.76</v>
-      </c>
-      <c r="V88" s="18" t="n">
-        <v>-3330.05</v>
-      </c>
-      <c r="W88" s="18" t="n">
-        <v>-1664.51</v>
-      </c>
-      <c r="X88" s="18" t="n">
-        <v>-1811.51</v>
-      </c>
-      <c r="Y88" s="18" t="n">
-        <v>-1869.28</v>
-      </c>
-      <c r="Z88" s="34" t="n">
-        <v>-8675.35</v>
-      </c>
-      <c r="AA88" s="18" t="n">
-        <v>-2587.67</v>
-      </c>
+      <c r="U88" s="9" t="n"/>
+      <c r="Z88" s="9" t="n"/>
       <c r="AB88" s="19" t="n">
-        <v>-1361.54</v>
+        <v>1758.92</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -18001,42 +17823,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>0</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="I89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="K89" s="9" t="n"/>
-      <c r="N89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P89" s="9" t="n"/>
-      <c r="S89" s="18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>1.18</v>
-      </c>
       <c r="U89" s="9" t="n"/>
-      <c r="X89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z89" s="9" t="n"/>
-      <c r="AB89" s="5" t="n"/>
+      <c r="AB89" s="19" t="n">
+        <v>323.72</v>
+      </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -18057,78 +17854,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>849.8099999999999</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>-592.47</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>-726.37</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>-473.36</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>-236.31</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>-2028.51</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>-674.8</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>-219.16</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>-94.27</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>-6.09</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>-994.3200000000001</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>-19.37</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>-18.24</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>-22.22</v>
-      </c>
-      <c r="T90" s="18" t="n">
-        <v>-101.78</v>
-      </c>
-      <c r="U90" s="34" t="n">
-        <v>-161.61</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>-190.33</v>
-      </c>
-      <c r="W90" s="18" t="n">
-        <v>-232.45</v>
-      </c>
-      <c r="X90" s="18" t="n">
-        <v>-67.31</v>
-      </c>
-      <c r="Y90" s="18" t="n">
-        <v>-267.92</v>
-      </c>
-      <c r="Z90" s="34" t="n">
-        <v>-758.01</v>
-      </c>
-      <c r="AA90" s="18" t="n">
-        <v>65.48</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
+      <c r="U90" s="9" t="n"/>
+      <c r="Z90" s="9" t="n"/>
       <c r="AB90" s="19" t="n">
-        <v>-69.28</v>
+        <v>141.87</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -18150,78 +17885,16 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>-3107.19</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>-2296.12</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>-2837.3</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>-2003.77</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>-11635.24</v>
-      </c>
-      <c r="K91" s="34" t="n">
-        <v>-18772.43</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>11073.44</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>-11492.17</v>
-      </c>
-      <c r="N91" s="18" t="n">
-        <v>3988.79</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>11972.66</v>
-      </c>
-      <c r="P91" s="34" t="n">
-        <v>15542.72</v>
-      </c>
-      <c r="Q91" s="18" t="n">
-        <v>-274.38</v>
-      </c>
-      <c r="R91" s="18" t="n">
-        <v>-2792.85</v>
-      </c>
-      <c r="S91" s="18" t="n">
-        <v>-470.05</v>
-      </c>
-      <c r="T91" s="18" t="n">
-        <v>8972.59</v>
-      </c>
-      <c r="U91" s="34" t="n">
-        <v>5435.31</v>
-      </c>
-      <c r="V91" s="18" t="n">
-        <v>9339.049999999999</v>
-      </c>
-      <c r="W91" s="18" t="n">
-        <v>-3549.15</v>
-      </c>
-      <c r="X91" s="18" t="n">
-        <v>-185.3</v>
-      </c>
-      <c r="Y91" s="18" t="n">
-        <v>2339.99</v>
-      </c>
-      <c r="Z91" s="34" t="n">
-        <v>7944.59</v>
-      </c>
-      <c r="AA91" s="18" t="n">
-        <v>11303.16</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
+      <c r="U91" s="9" t="n"/>
+      <c r="Z91" s="9" t="n"/>
       <c r="AB91" s="19" t="n">
-        <v>-2667.8</v>
+        <v>-156.46</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -18243,78 +17916,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>3301.56</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>1052.3</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>2078.92</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>1764.97</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>2093.24</v>
-      </c>
-      <c r="K92" s="34" t="n">
-        <v>6989.43</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>1667.33</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>2271.25</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>4628.97</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>1719.6</v>
-      </c>
-      <c r="P92" s="34" t="n">
-        <v>10287.15</v>
-      </c>
-      <c r="Q92" s="18" t="n">
-        <v>1107.78</v>
-      </c>
-      <c r="R92" s="18" t="n">
-        <v>2258.07</v>
-      </c>
-      <c r="S92" s="18" t="n">
-        <v>2744.78</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>3008.12</v>
-      </c>
-      <c r="U92" s="34" t="n">
-        <v>9118.75</v>
-      </c>
-      <c r="V92" s="18" t="n">
-        <v>2102.66</v>
-      </c>
-      <c r="W92" s="18" t="n">
-        <v>1136.44</v>
-      </c>
-      <c r="X92" s="18" t="n">
-        <v>2489.89</v>
-      </c>
-      <c r="Y92" s="18" t="n">
-        <v>1573.8</v>
-      </c>
-      <c r="Z92" s="34" t="n">
-        <v>7302.79</v>
-      </c>
-      <c r="AA92" s="18" t="n">
-        <v>395.98</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
+      <c r="U92" s="9" t="n"/>
+      <c r="Z92" s="9" t="n"/>
       <c r="AB92" s="19" t="n">
-        <v>2087.98</v>
+        <v>-16.74</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -18336,78 +17947,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>3301.56</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>1052.3</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>2078.92</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>1764.97</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>2093.24</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>6989.43</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>1667.33</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>2271.25</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>4628.97</v>
-      </c>
-      <c r="O93" s="18" t="n">
-        <v>1719.6</v>
-      </c>
-      <c r="P93" s="34" t="n">
-        <v>10287.15</v>
-      </c>
-      <c r="Q93" s="18" t="n">
-        <v>1107.78</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>2260.21</v>
-      </c>
-      <c r="S93" s="18" t="n">
-        <v>2744.78</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>3009</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>9121.77</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>2102.66</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>1136.44</v>
-      </c>
-      <c r="X93" s="18" t="n">
-        <v>2489.89</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>1573.8</v>
-      </c>
-      <c r="Z93" s="34" t="n">
-        <v>7302.79</v>
-      </c>
-      <c r="AA93" s="18" t="n">
-        <v>395.98</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
+      <c r="P93" s="9" t="n"/>
+      <c r="U93" s="9" t="n"/>
+      <c r="Z93" s="9" t="n"/>
       <c r="AB93" s="19" t="n">
-        <v>2087.98</v>
+        <v>0</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -18429,24 +17978,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>0</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="K94" s="9" t="n"/>
       <c r="P94" s="9" t="n"/>
-      <c r="S94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" s="18" t="n">
-        <v>0.88</v>
-      </c>
       <c r="U94" s="9" t="n"/>
       <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+      <c r="AB94" s="19" t="n">
+        <v>225.41</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -18467,24 +18009,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>0</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="K95" s="9" t="n"/>
       <c r="P95" s="9" t="n"/>
       <c r="U95" s="9" t="n"/>
-      <c r="X95" s="18" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="Y95" s="18" t="n">
-        <v>63.5</v>
-      </c>
       <c r="Z95" s="9" t="n"/>
-      <c r="AB95" s="5" t="n"/>
+      <c r="AB95" s="19" t="n">
+        <v>-1630.83</v>
+      </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -18505,78 +18040,78 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>-4681.06</v>
+        <v>-2675.54</v>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="18" t="n">
-        <v>5621.92</v>
+        <v>-1261.68</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>21267.43</v>
+        <v>-12165.09</v>
       </c>
       <c r="I96" s="18" t="n">
-        <v>-9963.440000000001</v>
+        <v>2442.21</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>9916.110000000001</v>
+        <v>8126.82</v>
       </c>
       <c r="K96" s="34" t="n">
-        <v>26842.02</v>
+        <v>-2857.74</v>
       </c>
       <c r="L96" s="18" t="n">
-        <v>-14398.52</v>
+        <v>-6154.45</v>
       </c>
       <c r="M96" s="18" t="n">
-        <v>-3880.71</v>
+        <v>20108.73</v>
       </c>
       <c r="N96" s="18" t="n">
-        <v>-9246.879999999999</v>
+        <v>4404.98</v>
       </c>
       <c r="O96" s="18" t="n">
-        <v>-18088.81</v>
+        <v>6219.3</v>
       </c>
       <c r="P96" s="34" t="n">
-        <v>-45614.92</v>
+        <v>24578.56</v>
       </c>
       <c r="Q96" s="18" t="n">
-        <v>6440.64</v>
+        <v>-5958.74</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>-11905.5</v>
+        <v>12271.57</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>-5979.83</v>
+        <v>-19295.86</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>-14787.17</v>
+        <v>32937.13</v>
       </c>
       <c r="U96" s="34" t="n">
-        <v>-26231.86</v>
+        <v>19954.1</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>-10909.43</v>
+        <v>3827.83</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>-31615.14</v>
+        <v>37329.48</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>-3124.24</v>
+        <v>-34.48</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>-2594.96</v>
+        <v>301.28</v>
       </c>
       <c r="Z96" s="34" t="n">
-        <v>-48243.77</v>
+        <v>41424.11</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>-1827.88</v>
+        <v>-12125.26</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>-10873.5</v>
+        <v>12030.08</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -18598,78 +18133,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
-        <v>42496.27</v>
+        <v>58.61</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>39715.61</v>
+        <v>40.16</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>64523.5</v>
+        <v>51.56</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>58473.97</v>
+        <v>-40.6</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>48432.47</v>
+        <v>11.38</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>211145.55</v>
+        <v>62.5</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>51492.5</v>
+        <v>32.55</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>64834.67</v>
+        <v>35.42</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>43852.77</v>
+        <v>181.25</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>32085.5</v>
+        <v>36.62</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>192265.44</v>
+        <v>285.84</v>
       </c>
       <c r="Q97" s="18" t="n">
-        <v>96221.95</v>
+        <v>56.29</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>62203.82</v>
+        <v>59.99</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>57545</v>
+        <v>33.57</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>34167.23</v>
+        <v>52.66</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>250138</v>
+        <v>202.51</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>68601.96000000001</v>
+        <v>177.65</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>33609.41</v>
+        <v>173.26</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>55762.81</v>
+        <v>207.26</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>46209.46</v>
+        <v>492.63</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>204183.64</v>
+        <v>1050.8</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>40567.28</v>
+        <v>146.78</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>35705.13</v>
+        <v>127.91</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -18691,41 +18226,71 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E98" s="18" t="n">
-        <v>0</v>
+        <v>-1357.25</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
-        <v>7000</v>
+        <v>-1437.3</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>6300</v>
+        <v>-1718.35</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>5000</v>
+        <v>-2036.47</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>103.15</v>
+        <v>-2608.64</v>
       </c>
       <c r="K98" s="34" t="n">
-        <v>18403.15</v>
-      </c>
-      <c r="N98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="18" t="n">
-        <v>6657.16</v>
+        <v>-7800.76</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>-2635.89</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>-2892.55</v>
       </c>
       <c r="P98" s="9" t="n"/>
+      <c r="Q98" s="18" t="n">
+        <v>-2821.94</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>-2758.24</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>-2723.2</v>
+      </c>
       <c r="T98" s="18" t="n">
-        <v>1687.06</v>
-      </c>
-      <c r="U98" s="9" t="n"/>
-      <c r="Z98" s="9" t="n"/>
-      <c r="AB98" s="5" t="n"/>
+        <v>-2348.38</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>-10651.76</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>-3330.05</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>-1664.51</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>-1811.51</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>-1869.28</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>-8675.35</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>-2587.67</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>-1361.54</v>
+      </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
       <c r="AE98" s="11" t="n"/>
@@ -18746,7 +18311,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>사채의증가</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E99" s="18" t="n">
@@ -18760,12 +18325,18 @@
         <v>0</v>
       </c>
       <c r="K99" s="9" t="n"/>
+      <c r="N99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P99" s="9" t="n"/>
       <c r="S99" s="18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U99" s="9" t="n"/>
       <c r="X99" s="18" t="n">
@@ -18796,78 +18367,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E100" s="18" t="n">
-        <v>47149.34</v>
+        <v>849.8099999999999</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="18" t="n">
-        <v>47800.73</v>
+        <v>-592.47</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>53272.38</v>
+        <v>-726.37</v>
       </c>
       <c r="I100" s="18" t="n">
-        <v>64665.7</v>
+        <v>-473.36</v>
       </c>
       <c r="J100" s="18" t="n">
-        <v>35872.39</v>
+        <v>-236.31</v>
       </c>
       <c r="K100" s="34" t="n">
-        <v>201611.2</v>
+        <v>-2028.51</v>
       </c>
       <c r="L100" s="18" t="n">
-        <v>63142.87</v>
+        <v>-674.8</v>
       </c>
       <c r="M100" s="18" t="n">
-        <v>72689.28</v>
+        <v>-219.16</v>
       </c>
       <c r="N100" s="18" t="n">
-        <v>47758.92</v>
+        <v>-94.27</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>49565.21</v>
+        <v>-6.09</v>
       </c>
       <c r="P100" s="34" t="n">
-        <v>233156.28</v>
+        <v>-994.3200000000001</v>
       </c>
       <c r="Q100" s="18" t="n">
-        <v>81474.89999999999</v>
+        <v>-19.37</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>67286.57000000001</v>
+        <v>-18.24</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>62183.19</v>
+        <v>-22.22</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>48530.85</v>
+        <v>-101.78</v>
       </c>
       <c r="U100" s="34" t="n">
-        <v>259475.51</v>
+        <v>-161.61</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>69315.21000000001</v>
+        <v>-190.33</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>62258.62</v>
+        <v>-232.45</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>58671.41</v>
+        <v>-67.31</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>54899.42</v>
+        <v>-267.92</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>245144.66</v>
+        <v>-758.01</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>42175.19</v>
+        <v>65.48</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>44770.42</v>
+        <v>-69.28</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -18889,30 +18460,79 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>사채의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0</v>
+        <v>-3107.19</v>
       </c>
       <c r="F101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
-      <c r="P101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>-2296.12</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>-2837.3</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>-2003.77</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>-11635.24</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>-18772.43</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>11073.44</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>-11492.17</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>3988.79</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>11972.66</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>15542.72</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>-274.38</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>-2792.85</v>
+      </c>
       <c r="S101" s="18" t="n">
-        <v>0</v>
+        <v>-470.05</v>
       </c>
       <c r="T101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" s="9" t="n"/>
+        <v>8972.59</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>5435.31</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>9339.049999999999</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>-3549.15</v>
+      </c>
       <c r="X101" s="18" t="n">
-        <v>0</v>
+        <v>-185.3</v>
       </c>
       <c r="Y101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="9" t="n"/>
-      <c r="AB101" s="5" t="n"/>
+        <v>2339.99</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>7944.59</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>11303.16</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>-2667.8</v>
+      </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
       <c r="AE101" s="11" t="n"/>
@@ -18933,78 +18553,78 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E102" s="18" t="n">
-        <v>324</v>
+        <v>3301.56</v>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="18" t="n">
-        <v>199.54</v>
+        <v>1052.3</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>289.51</v>
+        <v>2078.92</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>151.54</v>
+        <v>1764.97</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>155.4</v>
+        <v>2093.24</v>
       </c>
       <c r="K102" s="34" t="n">
-        <v>795.99</v>
+        <v>6989.43</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>147.06</v>
+        <v>1667.33</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>256.98</v>
+        <v>2271.25</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>126.88</v>
+        <v>4628.97</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>115.19</v>
+        <v>1719.6</v>
       </c>
       <c r="P102" s="34" t="n">
-        <v>646.11</v>
+        <v>10287.15</v>
       </c>
       <c r="Q102" s="18" t="n">
-        <v>131.42</v>
+        <v>1107.78</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>292.46</v>
+        <v>2258.07</v>
       </c>
       <c r="S102" s="18" t="n">
-        <v>224.52</v>
+        <v>2744.78</v>
       </c>
       <c r="T102" s="18" t="n">
-        <v>187.61</v>
+        <v>3008.12</v>
       </c>
       <c r="U102" s="34" t="n">
-        <v>836.01</v>
+        <v>9118.75</v>
       </c>
       <c r="V102" s="18" t="n">
-        <v>174.21</v>
+        <v>2102.66</v>
       </c>
       <c r="W102" s="18" t="n">
-        <v>333.23</v>
+        <v>1136.44</v>
       </c>
       <c r="X102" s="18" t="n">
-        <v>215.63</v>
+        <v>2489.89</v>
       </c>
       <c r="Y102" s="18" t="n">
-        <v>229.43</v>
+        <v>1573.8</v>
       </c>
       <c r="Z102" s="34" t="n">
-        <v>952.5</v>
+        <v>7302.79</v>
       </c>
       <c r="AA102" s="18" t="n">
-        <v>219.97</v>
+        <v>395.98</v>
       </c>
       <c r="AB102" s="19" t="n">
-        <v>208.2</v>
+        <v>2087.98</v>
       </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
@@ -19026,32 +18646,79 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0</v>
+        <v>3301.56</v>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
-      <c r="P103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>1052.3</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>2078.92</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>1764.97</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>2093.24</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>6989.43</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>1667.33</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>2271.25</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>4628.97</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>1719.6</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>10287.15</v>
+      </c>
       <c r="Q103" s="18" t="n">
-        <v>753.65</v>
+        <v>1107.78</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0</v>
+        <v>2260.21</v>
       </c>
       <c r="S103" s="18" t="n">
-        <v>0</v>
+        <v>2744.78</v>
       </c>
       <c r="T103" s="18" t="n">
-        <v>0</v>
+        <v>3009</v>
       </c>
       <c r="U103" s="34" t="n">
-        <v>753.65</v>
-      </c>
-      <c r="Z103" s="9" t="n"/>
-      <c r="AB103" s="5" t="n"/>
+        <v>9121.77</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>2102.66</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>1136.44</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>2489.89</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>1573.8</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>7302.79</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>395.98</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>2087.98</v>
+      </c>
       <c r="AC103" s="10" t="n"/>
       <c r="AD103" s="10" t="n"/>
       <c r="AE103" s="11" t="n"/>
@@ -19072,7 +18739,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E104" s="18" t="n">
@@ -19081,6 +18748,12 @@
       <c r="F104" s="9" t="n"/>
       <c r="K104" s="9" t="n"/>
       <c r="P104" s="9" t="n"/>
+      <c r="S104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="18" t="n">
+        <v>0.88</v>
+      </c>
       <c r="U104" s="9" t="n"/>
       <c r="Z104" s="9" t="n"/>
       <c r="AB104" s="5" t="n"/>
@@ -19104,74 +18777,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-10463.8</v>
+        <v>0</v>
       </c>
       <c r="F105" s="9" t="n"/>
-      <c r="G105" s="18" t="n">
-        <v>2064.12</v>
-      </c>
-      <c r="H105" s="18" t="n">
-        <v>6265.04</v>
-      </c>
-      <c r="I105" s="18" t="n">
-        <v>-9525</v>
-      </c>
-      <c r="J105" s="18" t="n">
-        <v>6407.69</v>
-      </c>
-      <c r="K105" s="34" t="n">
-        <v>5211.85</v>
-      </c>
-      <c r="L105" s="18" t="n">
-        <v>-9479.540000000001</v>
-      </c>
-      <c r="M105" s="18" t="n">
-        <v>4735.86</v>
-      </c>
-      <c r="N105" s="18" t="n">
-        <v>-853.11</v>
-      </c>
-      <c r="O105" s="18" t="n">
-        <v>-930.8</v>
-      </c>
-      <c r="P105" s="34" t="n">
-        <v>-6527.59</v>
-      </c>
-      <c r="Q105" s="18" t="n">
-        <v>207.52</v>
-      </c>
-      <c r="R105" s="18" t="n">
-        <v>-2420.22</v>
-      </c>
-      <c r="S105" s="18" t="n">
-        <v>220.31</v>
-      </c>
+      <c r="K105" s="9" t="n"/>
+      <c r="P105" s="9" t="n"/>
       <c r="U105" s="9" t="n"/>
-      <c r="V105" s="18" t="n">
-        <v>2257.44</v>
-      </c>
-      <c r="W105" s="18" t="n">
-        <v>2315.2</v>
-      </c>
       <c r="X105" s="18" t="n">
-        <v>-3344.02</v>
+        <v>71.5</v>
       </c>
       <c r="Y105" s="18" t="n">
-        <v>-103.69</v>
-      </c>
-      <c r="Z105" s="34" t="n">
-        <v>1124.93</v>
-      </c>
-      <c r="AA105" s="18" t="n">
-        <v>-2649.97</v>
-      </c>
-      <c r="AB105" s="19" t="n">
-        <v>-1511.23</v>
-      </c>
+        <v>63.5</v>
+      </c>
+      <c r="Z105" s="9" t="n"/>
+      <c r="AB105" s="5" t="n"/>
       <c r="AC105" s="10" t="n"/>
       <c r="AD105" s="10" t="n"/>
       <c r="AE105" s="11" t="n"/>
@@ -19192,78 +18815,78 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E106" s="18" t="n">
-        <v>-10428.14</v>
+        <v>-4681.06</v>
       </c>
       <c r="F106" s="9" t="n"/>
       <c r="G106" s="18" t="n">
-        <v>14196.15</v>
+        <v>5621.92</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>6468.92</v>
+        <v>21267.43</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>-9498.809999999999</v>
+        <v>-9963.440000000001</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>6141.84</v>
+        <v>9916.110000000001</v>
       </c>
       <c r="K106" s="34" t="n">
-        <v>17308.1</v>
+        <v>26842.02</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>7896</v>
+        <v>-14398.52</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>4756.42</v>
+        <v>-3880.71</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>-909.91</v>
+        <v>-9246.879999999999</v>
       </c>
       <c r="O106" s="18" t="n">
-        <v>-1048.86</v>
+        <v>-18088.81</v>
       </c>
       <c r="P106" s="34" t="n">
-        <v>10693.65</v>
+        <v>-45614.92</v>
       </c>
       <c r="Q106" s="18" t="n">
-        <v>10977.25</v>
+        <v>6440.64</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>-2478.98</v>
+        <v>-11905.5</v>
       </c>
       <c r="S106" s="18" t="n">
-        <v>221.55</v>
+        <v>-5979.83</v>
       </c>
       <c r="T106" s="18" t="n">
-        <v>1232.38</v>
+        <v>-14787.17</v>
       </c>
       <c r="U106" s="34" t="n">
-        <v>9952.200000000001</v>
+        <v>-26231.86</v>
       </c>
       <c r="V106" s="18" t="n">
-        <v>12303.56</v>
+        <v>-10909.43</v>
       </c>
       <c r="W106" s="18" t="n">
-        <v>2082.89</v>
+        <v>-31615.14</v>
       </c>
       <c r="X106" s="18" t="n">
-        <v>-3187.12</v>
+        <v>-3124.24</v>
       </c>
       <c r="Y106" s="18" t="n">
-        <v>-218.03</v>
+        <v>-2594.96</v>
       </c>
       <c r="Z106" s="34" t="n">
-        <v>10981.3</v>
+        <v>-48243.77</v>
       </c>
       <c r="AA106" s="18" t="n">
-        <v>8450.549999999999</v>
+        <v>-1827.88</v>
       </c>
       <c r="AB106" s="19" t="n">
-        <v>-1560.81</v>
+        <v>-10873.5</v>
       </c>
       <c r="AC106" s="10" t="n"/>
       <c r="AD106" s="10" t="n"/>
@@ -19285,63 +18908,79 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>42496.27</v>
       </c>
       <c r="F107" s="9" t="n"/>
       <c r="G107" s="18" t="n">
-        <v>245.34</v>
+        <v>39715.61</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>216.61</v>
+        <v>64523.5</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>154.55</v>
+        <v>58473.97</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>11.77</v>
+        <v>48432.47</v>
       </c>
       <c r="K107" s="34" t="n">
-        <v>628.27</v>
+        <v>211145.55</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>9.039999999999999</v>
+        <v>51492.5</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>358.79</v>
+        <v>64834.67</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>50.73</v>
+        <v>43852.77</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>8670.299999999999</v>
+        <v>32085.5</v>
       </c>
       <c r="P107" s="34" t="n">
-        <v>9088.860000000001</v>
+        <v>192265.44</v>
       </c>
       <c r="Q107" s="18" t="n">
-        <v>4.55</v>
+        <v>96221.95</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>0</v>
+        <v>62203.82</v>
       </c>
       <c r="S107" s="18" t="n">
-        <v>40.77</v>
+        <v>57545</v>
       </c>
       <c r="T107" s="18" t="n">
-        <v>4.73</v>
+        <v>34167.23</v>
       </c>
       <c r="U107" s="34" t="n">
-        <v>50.05</v>
+        <v>250138</v>
       </c>
       <c r="V107" s="18" t="n">
-        <v>461.49</v>
+        <v>68601.96000000001</v>
+      </c>
+      <c r="W107" s="18" t="n">
+        <v>33609.41</v>
       </c>
       <c r="X107" s="18" t="n">
-        <v>2341.86</v>
-      </c>
-      <c r="Z107" s="9" t="n"/>
-      <c r="AB107" s="5" t="n"/>
+        <v>55762.81</v>
+      </c>
+      <c r="Y107" s="18" t="n">
+        <v>46209.46</v>
+      </c>
+      <c r="Z107" s="34" t="n">
+        <v>204183.64</v>
+      </c>
+      <c r="AA107" s="18" t="n">
+        <v>40567.28</v>
+      </c>
+      <c r="AB107" s="19" t="n">
+        <v>35705.13</v>
+      </c>
       <c r="AC107" s="10" t="n"/>
       <c r="AD107" s="10" t="n"/>
       <c r="AE107" s="11" t="n"/>
@@ -19362,36 +19001,39 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>6300</v>
+      </c>
       <c r="I108" s="18" t="n">
-        <v>566.77</v>
+        <v>5000</v>
       </c>
       <c r="J108" s="18" t="n">
-        <v>551.85</v>
-      </c>
-      <c r="K108" s="9" t="n"/>
+        <v>103.15</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>18403.15</v>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="O108" s="18" t="n">
-        <v>3682.5</v>
+        <v>6657.16</v>
       </c>
       <c r="P108" s="9" t="n"/>
-      <c r="Q108" s="18" t="n">
-        <v>5333.33</v>
-      </c>
-      <c r="R108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="T108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="34" t="n">
-        <v>5333.33</v>
-      </c>
+        <v>1687.06</v>
+      </c>
+      <c r="U108" s="9" t="n"/>
       <c r="Z108" s="9" t="n"/>
       <c r="AB108" s="5" t="n"/>
       <c r="AC108" s="10" t="n"/>
@@ -19407,6 +19049,674 @@
       <c r="AM108" s="10" t="n"/>
       <c r="AN108" s="10" t="n"/>
       <c r="AO108" s="11" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="9" t="n"/>
+      <c r="I109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="9" t="n"/>
+      <c r="P109" s="9" t="n"/>
+      <c r="S109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="9" t="n"/>
+      <c r="X109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9" t="n"/>
+      <c r="AB109" s="5" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>47149.34</v>
+      </c>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="18" t="n">
+        <v>47800.73</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>53272.38</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>64665.7</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>35872.39</v>
+      </c>
+      <c r="K110" s="34" t="n">
+        <v>201611.2</v>
+      </c>
+      <c r="L110" s="18" t="n">
+        <v>63142.87</v>
+      </c>
+      <c r="M110" s="18" t="n">
+        <v>72689.28</v>
+      </c>
+      <c r="N110" s="18" t="n">
+        <v>47758.92</v>
+      </c>
+      <c r="O110" s="18" t="n">
+        <v>49565.21</v>
+      </c>
+      <c r="P110" s="34" t="n">
+        <v>233156.28</v>
+      </c>
+      <c r="Q110" s="18" t="n">
+        <v>81474.89999999999</v>
+      </c>
+      <c r="R110" s="18" t="n">
+        <v>67286.57000000001</v>
+      </c>
+      <c r="S110" s="18" t="n">
+        <v>62183.19</v>
+      </c>
+      <c r="T110" s="18" t="n">
+        <v>48530.85</v>
+      </c>
+      <c r="U110" s="34" t="n">
+        <v>259475.51</v>
+      </c>
+      <c r="V110" s="18" t="n">
+        <v>69315.21000000001</v>
+      </c>
+      <c r="W110" s="18" t="n">
+        <v>62258.62</v>
+      </c>
+      <c r="X110" s="18" t="n">
+        <v>58671.41</v>
+      </c>
+      <c r="Y110" s="18" t="n">
+        <v>54899.42</v>
+      </c>
+      <c r="Z110" s="34" t="n">
+        <v>245144.66</v>
+      </c>
+      <c r="AA110" s="18" t="n">
+        <v>42175.19</v>
+      </c>
+      <c r="AB110" s="19" t="n">
+        <v>44770.42</v>
+      </c>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="10" t="n"/>
+      <c r="AL110" s="10" t="n"/>
+      <c r="AM110" s="10" t="n"/>
+      <c r="AN110" s="10" t="n"/>
+      <c r="AO110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
+      <c r="P111" s="9" t="n"/>
+      <c r="S111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" s="9" t="n"/>
+      <c r="X111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9" t="n"/>
+      <c r="AB111" s="5" t="n"/>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="11" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>324</v>
+      </c>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="18" t="n">
+        <v>199.54</v>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>289.51</v>
+      </c>
+      <c r="I112" s="18" t="n">
+        <v>151.54</v>
+      </c>
+      <c r="J112" s="18" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="K112" s="34" t="n">
+        <v>795.99</v>
+      </c>
+      <c r="L112" s="18" t="n">
+        <v>147.06</v>
+      </c>
+      <c r="M112" s="18" t="n">
+        <v>256.98</v>
+      </c>
+      <c r="N112" s="18" t="n">
+        <v>126.88</v>
+      </c>
+      <c r="O112" s="18" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="P112" s="34" t="n">
+        <v>646.11</v>
+      </c>
+      <c r="Q112" s="18" t="n">
+        <v>131.42</v>
+      </c>
+      <c r="R112" s="18" t="n">
+        <v>292.46</v>
+      </c>
+      <c r="S112" s="18" t="n">
+        <v>224.52</v>
+      </c>
+      <c r="T112" s="18" t="n">
+        <v>187.61</v>
+      </c>
+      <c r="U112" s="34" t="n">
+        <v>836.01</v>
+      </c>
+      <c r="V112" s="18" t="n">
+        <v>174.21</v>
+      </c>
+      <c r="W112" s="18" t="n">
+        <v>333.23</v>
+      </c>
+      <c r="X112" s="18" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="Y112" s="18" t="n">
+        <v>229.43</v>
+      </c>
+      <c r="Z112" s="34" t="n">
+        <v>952.5</v>
+      </c>
+      <c r="AA112" s="18" t="n">
+        <v>219.97</v>
+      </c>
+      <c r="AB112" s="19" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="10" t="n"/>
+      <c r="AL112" s="10" t="n"/>
+      <c r="AM112" s="10" t="n"/>
+      <c r="AN112" s="10" t="n"/>
+      <c r="AO112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="9" t="n"/>
+      <c r="K113" s="9" t="n"/>
+      <c r="P113" s="9" t="n"/>
+      <c r="Q113" s="18" t="n">
+        <v>753.65</v>
+      </c>
+      <c r="R113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="34" t="n">
+        <v>753.65</v>
+      </c>
+      <c r="Z113" s="9" t="n"/>
+      <c r="AB113" s="5" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
+      <c r="P114" s="9" t="n"/>
+      <c r="U114" s="9" t="n"/>
+      <c r="Z114" s="9" t="n"/>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="10" t="n"/>
+      <c r="AL114" s="10" t="n"/>
+      <c r="AM114" s="10" t="n"/>
+      <c r="AN114" s="10" t="n"/>
+      <c r="AO114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="n">
+        <v>-10463.8</v>
+      </c>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="18" t="n">
+        <v>2064.12</v>
+      </c>
+      <c r="H115" s="18" t="n">
+        <v>6265.04</v>
+      </c>
+      <c r="I115" s="18" t="n">
+        <v>-9525</v>
+      </c>
+      <c r="J115" s="18" t="n">
+        <v>6407.69</v>
+      </c>
+      <c r="K115" s="34" t="n">
+        <v>5211.85</v>
+      </c>
+      <c r="L115" s="18" t="n">
+        <v>-9479.540000000001</v>
+      </c>
+      <c r="M115" s="18" t="n">
+        <v>4735.86</v>
+      </c>
+      <c r="N115" s="18" t="n">
+        <v>-853.11</v>
+      </c>
+      <c r="O115" s="18" t="n">
+        <v>-930.8</v>
+      </c>
+      <c r="P115" s="34" t="n">
+        <v>-6527.59</v>
+      </c>
+      <c r="Q115" s="18" t="n">
+        <v>207.52</v>
+      </c>
+      <c r="R115" s="18" t="n">
+        <v>-2420.22</v>
+      </c>
+      <c r="S115" s="18" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="U115" s="9" t="n"/>
+      <c r="V115" s="18" t="n">
+        <v>2257.44</v>
+      </c>
+      <c r="W115" s="18" t="n">
+        <v>2315.2</v>
+      </c>
+      <c r="X115" s="18" t="n">
+        <v>-3344.02</v>
+      </c>
+      <c r="Y115" s="18" t="n">
+        <v>-103.69</v>
+      </c>
+      <c r="Z115" s="34" t="n">
+        <v>1124.93</v>
+      </c>
+      <c r="AA115" s="18" t="n">
+        <v>-2649.97</v>
+      </c>
+      <c r="AB115" s="19" t="n">
+        <v>-1511.23</v>
+      </c>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="10" t="n"/>
+      <c r="AL115" s="10" t="n"/>
+      <c r="AM115" s="10" t="n"/>
+      <c r="AN115" s="10" t="n"/>
+      <c r="AO115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="n">
+        <v>-10428.14</v>
+      </c>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="18" t="n">
+        <v>14196.15</v>
+      </c>
+      <c r="H116" s="18" t="n">
+        <v>6468.92</v>
+      </c>
+      <c r="I116" s="18" t="n">
+        <v>-9498.809999999999</v>
+      </c>
+      <c r="J116" s="18" t="n">
+        <v>6141.84</v>
+      </c>
+      <c r="K116" s="34" t="n">
+        <v>17308.1</v>
+      </c>
+      <c r="L116" s="18" t="n">
+        <v>7896</v>
+      </c>
+      <c r="M116" s="18" t="n">
+        <v>4756.42</v>
+      </c>
+      <c r="N116" s="18" t="n">
+        <v>-909.91</v>
+      </c>
+      <c r="O116" s="18" t="n">
+        <v>-1048.86</v>
+      </c>
+      <c r="P116" s="34" t="n">
+        <v>10693.65</v>
+      </c>
+      <c r="Q116" s="18" t="n">
+        <v>10977.25</v>
+      </c>
+      <c r="R116" s="18" t="n">
+        <v>-2478.98</v>
+      </c>
+      <c r="S116" s="18" t="n">
+        <v>221.55</v>
+      </c>
+      <c r="T116" s="18" t="n">
+        <v>1232.38</v>
+      </c>
+      <c r="U116" s="34" t="n">
+        <v>9952.200000000001</v>
+      </c>
+      <c r="V116" s="18" t="n">
+        <v>12303.56</v>
+      </c>
+      <c r="W116" s="18" t="n">
+        <v>2082.89</v>
+      </c>
+      <c r="X116" s="18" t="n">
+        <v>-3187.12</v>
+      </c>
+      <c r="Y116" s="18" t="n">
+        <v>-218.03</v>
+      </c>
+      <c r="Z116" s="34" t="n">
+        <v>10981.3</v>
+      </c>
+      <c r="AA116" s="18" t="n">
+        <v>8450.549999999999</v>
+      </c>
+      <c r="AB116" s="19" t="n">
+        <v>-1560.81</v>
+      </c>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="10" t="n"/>
+      <c r="AL116" s="10" t="n"/>
+      <c r="AM116" s="10" t="n"/>
+      <c r="AN116" s="10" t="n"/>
+      <c r="AO116" s="11" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="18" t="n">
+        <v>245.34</v>
+      </c>
+      <c r="H117" s="18" t="n">
+        <v>216.61</v>
+      </c>
+      <c r="I117" s="18" t="n">
+        <v>154.55</v>
+      </c>
+      <c r="J117" s="18" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="K117" s="34" t="n">
+        <v>628.27</v>
+      </c>
+      <c r="L117" s="18" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M117" s="18" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="N117" s="18" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="O117" s="18" t="n">
+        <v>8670.299999999999</v>
+      </c>
+      <c r="P117" s="34" t="n">
+        <v>9088.860000000001</v>
+      </c>
+      <c r="Q117" s="18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R117" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" s="18" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="T117" s="18" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="U117" s="34" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="V117" s="18" t="n">
+        <v>461.49</v>
+      </c>
+      <c r="X117" s="18" t="n">
+        <v>2341.86</v>
+      </c>
+      <c r="Z117" s="9" t="n"/>
+      <c r="AB117" s="5" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="10" t="n"/>
+      <c r="AL117" s="10" t="n"/>
+      <c r="AM117" s="10" t="n"/>
+      <c r="AN117" s="10" t="n"/>
+      <c r="AO117" s="11" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="n"/>
+      <c r="I118" s="18" t="n">
+        <v>566.77</v>
+      </c>
+      <c r="J118" s="18" t="n">
+        <v>551.85</v>
+      </c>
+      <c r="K118" s="9" t="n"/>
+      <c r="O118" s="18" t="n">
+        <v>3682.5</v>
+      </c>
+      <c r="P118" s="9" t="n"/>
+      <c r="Q118" s="18" t="n">
+        <v>5333.33</v>
+      </c>
+      <c r="R118" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" s="34" t="n">
+        <v>5333.33</v>
+      </c>
+      <c r="Z118" s="9" t="n"/>
+      <c r="AB118" s="5" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="11" t="n"/>
+      <c r="AK118" s="10" t="n"/>
+      <c r="AL118" s="10" t="n"/>
+      <c r="AM118" s="10" t="n"/>
+      <c r="AN118" s="10" t="n"/>
+      <c r="AO118" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19667,7 +19977,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4629,7 +4629,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5500,35 +5500,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5619,35 +5619,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5738,35 +5738,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5857,35 +5857,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5976,35 +5976,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6095,35 +6095,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6214,35 +6214,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6333,35 +6333,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6468,7 +6468,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2235</v>
+        <v>2180</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6741,7 +6741,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2175</v>
+        <v>2176.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>2235</v>
+        <v>2180</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.078475197538492</v>
+        <v>0.07847519753849203</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.09303260255191068</v>
+        <v>0.09303260255191062</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35756,7 +35756,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41273,7 +41273,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43552,7 +43552,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4629,7 +4629,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5500,35 +5500,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5619,35 +5619,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5738,35 +5738,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5857,35 +5857,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5976,35 +5976,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6095,35 +6095,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6214,35 +6214,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6333,35 +6333,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6468,7 +6468,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2180</v>
+        <v>2095</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6741,7 +6741,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2176.7</v>
+        <v>2151.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10022,11 +10022,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>2180</v>
+        <v>2095</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,075원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,160원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35756,7 +35756,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41273,7 +41273,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43552,7 +43552,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4629,7 +4629,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -5500,35 +5500,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5619,35 +5619,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5738,35 +5738,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5857,35 +5857,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5976,35 +5976,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6095,35 +6095,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6214,35 +6214,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6333,35 +6333,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6468,7 +6468,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2095</v>
+        <v>2200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6741,7 +6741,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2151.2</v>
+        <v>2177</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10022,11 +10022,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>2095</v>
+        <v>2200</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,160원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,105원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -35756,7 +35756,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41273,7 +41273,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43552,7 +43552,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1734,79 +1734,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AI43" authorId="0" shapeId="0">
+    <comment ref="AI42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AN43" authorId="0" shapeId="0">
+    <comment ref="AN42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
@@ -3474,92 +3414,92 @@
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="G33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="I33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="L33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="M33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="N33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="O33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Q33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,501,846주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="R33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,170,303주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="S33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,170,303주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="T33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,170,303주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="V33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,170,303주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="W33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,170,303주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="X33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,170,303주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Y33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,103,517주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AA33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 68,103,517주 × 1/5(환산 — 2026Q2 1/5 수동(복합 사건); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AB33" authorId="0" shapeId="0">
@@ -3687,159 +3627,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="Y35" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI -116억 − (비영업손익 -237억 − 12분기 기준선 -33억) × (1 − 22.9%, 모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)) × 지배 비중 0.93(그 분기 지배NI/NI) = 30억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS -170.2원</t>
-      </text>
-    </comment>
-    <comment ref="AA35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AB35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 -204억 × (1 − 세율 22.9% [모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)]) × 지배 비중 0.9315 [그 분기 지배NI/NI] = 30억 ÷ 유통주식수 · 초과 = 비영업손익 -237억 − 12분기 기준선 -33억 · 보고 EPS -851원(EPS 행 불변) · 상수 -156.9·0.9315 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC36" authorId="0" shapeId="0">
@@ -4613,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4629,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4517,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4792,50 +4642,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2025Q4 보고 -851→조정 222원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 1개 &lt; 4)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/012160.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/012160.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 -237억(영업이익 -22억의 11배, 12분기 중위 33억·기준선 -33억) → 지배NI -116억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 44.4원(보고 -170.2원; 초과 비영업손익 -204억 × (1 − 세율 22.9%) × 지배 비중 0.93 = -146억 차감 — 추정, 조정EPS 행)</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 주식수 사건 환산: 2026Q2 1/5 수동(복합 사건)(eps_reported 교차검증 confirmed) → 사건 전 실적 18분기의 주식수·EPS·BPS·DPS 를 비율 환산(IAS 33.64; 셀 kind estimate, basis 에 원주식수·비율) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 -237억(영업이익 -22억의 11배, 12분기 중위 33억·기준선 -33억) → 지배NI -116억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 221.9원(보고 -851.1원; 초과 비영업손익 -204억 × (1 − 세율 22.9%) × 지배 비중 0.93 = -146억 차감 — 추정, 조정EPS 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 2.5, "op_wape_pct": 86.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 1092.86, "rev_act": 1098.95, "op_pred": -9.26, "op_act": -69.66}, {"q": "2025Q4", "rev_pred": 1004.22, "rev_act": 963.22, "op_pred": -8.51, "op_act": -22.38}, {"q": "2026Q1", "rev_pred": 1019.23, "rev_act": 964.25, "op_pred": -8.63, "op_act": -14.39}, {"q": "2026Q2", "rev_pred": 1067.88, "rev_act": 1067.67, "op_pred": -9.05, "op_act": 21.74}]}</t>
         </is>
@@ -4852,7 +4709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:AO60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7039,11 +6896,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -7051,19 +6908,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -7071,19 +6928,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -8289,11 +8146,11 @@
         <v/>
       </c>
       <c r="AC30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AD30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AE30" s="25">
@@ -8301,19 +8158,19 @@
         <v/>
       </c>
       <c r="AF30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AG30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AH30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AI30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AJ30" s="25">
@@ -8321,19 +8178,19 @@
         <v/>
       </c>
       <c r="AK30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AL30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AM30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AN30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AO30" s="25">
@@ -9701,264 +9558,176 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="22" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21">
-        <f>IFERROR(subQ!J35/subQ!E35-1,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="22" t="n"/>
-      <c r="L42" s="21">
-        <f>IFERROR(subQ!L35/subQ!G35-1,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="21">
-        <f>IFERROR(subQ!M35/subQ!H35-1,"")</f>
-        <v/>
-      </c>
-      <c r="N42" s="21">
-        <f>IFERROR(subQ!N35/subQ!I35-1,"")</f>
-        <v/>
-      </c>
-      <c r="O42" s="21">
-        <f>IFERROR(subQ!O35/subQ!J35-1,"")</f>
-        <v/>
-      </c>
-      <c r="P42" s="22" t="n"/>
-      <c r="Q42" s="21">
-        <f>IFERROR(subQ!Q35/subQ!L35-1,"")</f>
-        <v/>
-      </c>
-      <c r="R42" s="21">
-        <f>IFERROR(subQ!R35/subQ!M35-1,"")</f>
-        <v/>
-      </c>
-      <c r="S42" s="21">
-        <f>IFERROR(subQ!S35/subQ!N35-1,"")</f>
-        <v/>
-      </c>
-      <c r="T42" s="21">
-        <f>IFERROR(subQ!T35/subQ!O35-1,"")</f>
-        <v/>
-      </c>
-      <c r="U42" s="22" t="n"/>
-      <c r="V42" s="21">
-        <f>IFERROR(subQ!V35/subQ!Q35-1,"")</f>
-        <v/>
-      </c>
-      <c r="W42" s="21">
-        <f>IFERROR(subQ!W35/subQ!R35-1,"")</f>
-        <v/>
-      </c>
-      <c r="X42" s="21">
-        <f>IFERROR(subQ!X35/subQ!S35-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y42" s="21">
-        <f>IFERROR(subQ!Y35/subQ!T35-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z42" s="22" t="n"/>
-      <c r="AA42" s="21">
-        <f>IFERROR(subQ!AA35/subQ!V35-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB42" s="23">
-        <f>IFERROR(subQ!AB35/subQ!W35-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC42" s="24" t="n">
-        <v>-0.045364107</v>
-      </c>
-      <c r="AD42" s="24" t="n">
-        <v>-6.182432432</v>
-      </c>
-      <c r="AE42" s="25" t="n"/>
-      <c r="AF42" s="24" t="n">
-        <v>16.984732824</v>
-      </c>
-      <c r="AG42" s="24" t="n">
-        <v>-88.172413793</v>
-      </c>
-      <c r="AH42" s="24" t="n">
-        <v>0.066694456</v>
-      </c>
-      <c r="AI42" s="24" t="n">
-        <v>0.074315515</v>
-      </c>
-      <c r="AJ42" s="25" t="n"/>
-      <c r="AK42" s="24" t="n">
-        <v>0.074278438</v>
-      </c>
-      <c r="AL42" s="24" t="n">
-        <v>0.068433544</v>
-      </c>
-      <c r="AM42" s="24" t="n">
-        <v>0.08167252799999999</v>
-      </c>
-      <c r="AN42" s="24" t="n">
-        <v>0.08778317200000001</v>
-      </c>
-      <c r="AO42" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E42" s="27">
+        <f>subQ!E37</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>subQ!F37</f>
+        <v/>
+      </c>
+      <c r="G42" s="27">
+        <f>subQ!G37</f>
+        <v/>
+      </c>
+      <c r="H42" s="27">
+        <f>subQ!H37</f>
+        <v/>
+      </c>
+      <c r="I42" s="27">
+        <f>subQ!I37</f>
+        <v/>
+      </c>
+      <c r="J42" s="27">
+        <f>subQ!J37</f>
+        <v/>
+      </c>
+      <c r="K42" s="28">
+        <f>subQ!K37</f>
+        <v/>
+      </c>
+      <c r="L42" s="27">
+        <f>subQ!L37</f>
+        <v/>
+      </c>
+      <c r="M42" s="27">
+        <f>subQ!M37</f>
+        <v/>
+      </c>
+      <c r="N42" s="27">
+        <f>subQ!N37</f>
+        <v/>
+      </c>
+      <c r="O42" s="27">
+        <f>subQ!O37</f>
+        <v/>
+      </c>
+      <c r="P42" s="28">
+        <f>subQ!P37</f>
+        <v/>
+      </c>
+      <c r="Q42" s="27">
+        <f>subQ!Q37</f>
+        <v/>
+      </c>
+      <c r="R42" s="27">
+        <f>subQ!R37</f>
+        <v/>
+      </c>
+      <c r="S42" s="27">
+        <f>subQ!S37</f>
+        <v/>
+      </c>
+      <c r="T42" s="27">
+        <f>subQ!T37</f>
+        <v/>
+      </c>
+      <c r="U42" s="28">
+        <f>subQ!U37</f>
+        <v/>
+      </c>
+      <c r="V42" s="27">
+        <f>subQ!V37</f>
+        <v/>
+      </c>
+      <c r="W42" s="27">
+        <f>subQ!W37</f>
+        <v/>
+      </c>
+      <c r="X42" s="27">
+        <f>subQ!X37</f>
+        <v/>
+      </c>
+      <c r="Y42" s="27">
+        <f>subQ!Y37</f>
+        <v/>
+      </c>
+      <c r="Z42" s="28">
+        <f>subQ!Z37</f>
+        <v/>
+      </c>
+      <c r="AA42" s="27">
+        <f>subQ!AA37</f>
+        <v/>
+      </c>
+      <c r="AB42" s="29">
+        <f>subQ!AB37</f>
+        <v/>
+      </c>
+      <c r="AC42" s="32" t="n"/>
+      <c r="AD42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="31">
+        <f>subQ!AE37</f>
+        <v/>
+      </c>
+      <c r="AF42" s="32" t="n"/>
+      <c r="AG42" s="32" t="n"/>
+      <c r="AH42" s="32" t="n"/>
+      <c r="AI42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="31">
+        <f>subQ!AJ37</f>
+        <v/>
+      </c>
+      <c r="AK42" s="32" t="n"/>
+      <c r="AL42" s="32" t="n"/>
+      <c r="AM42" s="32" t="n"/>
+      <c r="AN42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="31">
+        <f>subQ!AO37</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E43" s="27">
-        <f>subQ!E37</f>
-        <v/>
-      </c>
-      <c r="F43" s="28">
-        <f>subQ!F37</f>
-        <v/>
-      </c>
-      <c r="G43" s="27">
-        <f>subQ!G37</f>
-        <v/>
-      </c>
-      <c r="H43" s="27">
-        <f>subQ!H37</f>
-        <v/>
-      </c>
-      <c r="I43" s="27">
-        <f>subQ!I37</f>
-        <v/>
-      </c>
-      <c r="J43" s="27">
-        <f>subQ!J37</f>
-        <v/>
-      </c>
-      <c r="K43" s="28">
-        <f>subQ!K37</f>
-        <v/>
-      </c>
-      <c r="L43" s="27">
-        <f>subQ!L37</f>
-        <v/>
-      </c>
-      <c r="M43" s="27">
-        <f>subQ!M37</f>
-        <v/>
-      </c>
-      <c r="N43" s="27">
-        <f>subQ!N37</f>
-        <v/>
-      </c>
-      <c r="O43" s="27">
-        <f>subQ!O37</f>
-        <v/>
-      </c>
-      <c r="P43" s="28">
-        <f>subQ!P37</f>
-        <v/>
-      </c>
-      <c r="Q43" s="27">
-        <f>subQ!Q37</f>
-        <v/>
-      </c>
-      <c r="R43" s="27">
-        <f>subQ!R37</f>
-        <v/>
-      </c>
-      <c r="S43" s="27">
-        <f>subQ!S37</f>
-        <v/>
-      </c>
-      <c r="T43" s="27">
-        <f>subQ!T37</f>
-        <v/>
-      </c>
-      <c r="U43" s="28">
-        <f>subQ!U37</f>
-        <v/>
-      </c>
-      <c r="V43" s="27">
-        <f>subQ!V37</f>
-        <v/>
-      </c>
-      <c r="W43" s="27">
-        <f>subQ!W37</f>
-        <v/>
-      </c>
-      <c r="X43" s="27">
-        <f>subQ!X37</f>
-        <v/>
-      </c>
-      <c r="Y43" s="27">
-        <f>subQ!Y37</f>
-        <v/>
-      </c>
-      <c r="Z43" s="28">
-        <f>subQ!Z37</f>
-        <v/>
-      </c>
-      <c r="AA43" s="27">
-        <f>subQ!AA37</f>
-        <v/>
-      </c>
-      <c r="AB43" s="29">
-        <f>subQ!AB37</f>
-        <v/>
-      </c>
-      <c r="AC43" s="32" t="n"/>
-      <c r="AD43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="31">
-        <f>subQ!AE37</f>
-        <v/>
-      </c>
-      <c r="AF43" s="32" t="n"/>
-      <c r="AG43" s="32" t="n"/>
-      <c r="AH43" s="32" t="n"/>
-      <c r="AI43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="31">
-        <f>subQ!AJ37</f>
-        <v/>
-      </c>
-      <c r="AK43" s="32" t="n"/>
-      <c r="AL43" s="32" t="n"/>
-      <c r="AM43" s="32" t="n"/>
-      <c r="AN43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="31">
-        <f>subQ!AO37</f>
-        <v/>
-      </c>
+      <c r="F43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AB43" s="5" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="10" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="11" t="n"/>
+      <c r="AK43" s="10" t="n"/>
+      <c r="AL43" s="10" t="n"/>
+      <c r="AM43" s="10" t="n"/>
+      <c r="AN43" s="10" t="n"/>
+      <c r="AO43" s="11" t="n"/>
     </row>
     <row r="44">
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
@@ -9980,14 +9749,22 @@
       <c r="AO44" s="11" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,105원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -10013,20 +9790,22 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D46" s="34" t="n">
-        <v>2200</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,105원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10052,22 +9831,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D47" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10093,20 +9870,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 1개 &lt; 4)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -10132,20 +9909,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D49" s="30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 1개 &lt; 4)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -10171,20 +9948,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D50" s="30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -10210,20 +9987,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="n">
-        <v>20</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -10249,20 +10026,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D52" s="36" t="n">
+        <v>0.2291</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 세전 합 ≤ 0 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 2분기(2025Q1~2026Q2)의 법인세/세전 중위 22.9%</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -10288,20 +10065,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2291</v>
+        <v>0.078475197538492</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 세전 합 ≤ 0 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 2분기(2025Q1~2026Q2)의 법인세/세전 중위 22.9%</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0785)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -10327,20 +10104,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.07847519753849203</v>
+        <v>1</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0785)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -10366,20 +10143,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>1</v>
+        <v>0.09303260255191068</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.093)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -10405,20 +10182,20 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.09303260255191062</v>
+        <v>0.05698268810235374</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.093)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.057)</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -10444,20 +10221,18 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D57" s="36" t="n">
-        <v>0.05698268810235374</v>
-      </c>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.057)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -10483,18 +10258,18 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="n"/>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
@@ -10520,18 +10295,18 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D59" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
@@ -10557,15 +10332,15 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -10590,43 +10365,6 @@
       <c r="AM60" s="10" t="n"/>
       <c r="AN60" s="10" t="n"/>
       <c r="AO60" s="11" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="n"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
-      <c r="Z61" s="9" t="n"/>
-      <c r="AB61" s="5" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="11" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="11" t="n"/>
-      <c r="AK61" s="10" t="n"/>
-      <c r="AL61" s="10" t="n"/>
-      <c r="AM61" s="10" t="n"/>
-      <c r="AN61" s="10" t="n"/>
-      <c r="AO61" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10888,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13495,28 +13233,28 @@
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>643.73</v>
+        <v>1183.41</v>
       </c>
       <c r="F30" s="37" t="n">
-        <v>643.73</v>
+        <v>1183.41</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>545.96</v>
+        <v>986.04</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>526.3</v>
+        <v>1208.14</v>
       </c>
       <c r="I30" s="18" t="n">
-        <v>469.47</v>
+        <v>1078.99</v>
       </c>
       <c r="J30" s="18" t="n">
-        <v>553.75</v>
+        <v>1148.65</v>
       </c>
       <c r="K30" s="37" t="n">
-        <v>553.75</v>
+        <v>1148.65</v>
       </c>
       <c r="L30" s="18" t="n">
-        <v>585.7</v>
+        <v>1161.74</v>
       </c>
       <c r="M30" s="18" t="n">
         <v>844.8200000000001</v>
@@ -13546,13 +13284,13 @@
         <v>1218.7</v>
       </c>
       <c r="V30" s="18" t="n">
-        <v>602.3200000000001</v>
+        <v>1216.17</v>
       </c>
       <c r="W30" s="18" t="n">
-        <v>729.55</v>
+        <v>1838.53</v>
       </c>
       <c r="X30" s="18" t="n">
-        <v>712.37</v>
+        <v>1821.37</v>
       </c>
       <c r="Y30" s="18" t="n">
         <v>1931.05</v>
@@ -13561,7 +13299,7 @@
         <v>1931.05</v>
       </c>
       <c r="AA30" s="18" t="n">
-        <v>578.22</v>
+        <v>1024.27</v>
       </c>
       <c r="AB30" s="19" t="n">
         <v>1018.65</v>
@@ -14290,15 +14028,29 @@
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>1927.74</v>
+        <v>2467.42</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>1927.74</v>
+        <v>2467.42</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>3940.54</v>
-      </c>
-      <c r="K39" s="9" t="n"/>
+        <v>4380.62</v>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>681.84</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>609.52</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>594.9</v>
+      </c>
+      <c r="K39" s="37" t="n">
+        <v>594.9</v>
+      </c>
+      <c r="L39" s="18" t="n">
+        <v>576.04</v>
+      </c>
       <c r="M39" s="18" t="n">
         <v>376.64</v>
       </c>
@@ -14326,6 +14078,15 @@
       <c r="U39" s="37" t="n">
         <v>651.5</v>
       </c>
+      <c r="V39" s="18" t="n">
+        <v>613.85</v>
+      </c>
+      <c r="W39" s="18" t="n">
+        <v>1108.98</v>
+      </c>
+      <c r="X39" s="18" t="n">
+        <v>1109</v>
+      </c>
       <c r="Y39" s="18" t="n">
         <v>3161.72</v>
       </c>
@@ -14333,7 +14094,7 @@
         <v>3161.72</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>1760.05</v>
+        <v>2206.1</v>
       </c>
       <c r="AB39" s="19" t="n">
         <v>2374.94</v>
@@ -14358,80 +14119,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>6523.25</v>
+        <v>539.6799999999999</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>6523.25</v>
+        <v>539.6799999999999</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>7047.83</v>
+        <v>440.08</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>7607.14</v>
+        <v>681.84</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>7892.69</v>
+        <v>609.52</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>5165.28</v>
+        <v>594.9</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>5165.28</v>
+        <v>594.9</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>5179.48</v>
+        <v>576.04</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>4948.89</v>
+        <v>376.64</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>5146.41</v>
+        <v>565</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>5863.45</v>
+        <v>527.1900000000001</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>5863.45</v>
+        <v>527.1900000000001</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>6367.1</v>
+        <v>1028.71</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>6962.3</v>
+        <v>814.12</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>7706.65</v>
+        <v>686.25</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>9427.280000000001</v>
+        <v>651.5</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>9427.280000000001</v>
+        <v>651.5</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>9537.120000000001</v>
+        <v>613.85</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>9608.67</v>
+        <v>1108.98</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>8794.92</v>
+        <v>1109</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>7894.87</v>
+        <v>1070.62</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>7894.87</v>
+        <v>1070.62</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>8259.379999999999</v>
+        <v>446.05</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>8944.84</v>
+        <v>389.48</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -14453,80 +14214,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>13326.19</v>
+        <v>6523.25</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>13326.19</v>
+        <v>6523.25</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>12648.92</v>
+        <v>7047.83</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>12775.08</v>
+        <v>7607.14</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>12429.39</v>
+        <v>7892.69</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>11620.34</v>
+        <v>5165.28</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>11620.34</v>
+        <v>5165.28</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>11502.21</v>
+        <v>5179.48</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>12054.79</v>
+        <v>4948.89</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>11954.55</v>
+        <v>5146.41</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>21317.29</v>
+        <v>5863.45</v>
       </c>
       <c r="P41" s="37" t="n">
-        <v>21317.29</v>
+        <v>5863.45</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>22023.49</v>
+        <v>6367.1</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>20964.84</v>
+        <v>6962.3</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>21523.47</v>
+        <v>7706.65</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>21557.75</v>
+        <v>9427.280000000001</v>
       </c>
       <c r="U41" s="37" t="n">
-        <v>21557.75</v>
+        <v>9427.280000000001</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>21483.76</v>
+        <v>9537.120000000001</v>
       </c>
       <c r="W41" s="18" t="n">
-        <v>15376.15</v>
+        <v>9608.67</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>21335.78</v>
+        <v>8794.92</v>
       </c>
       <c r="Y41" s="18" t="n">
-        <v>9327.68</v>
+        <v>7894.87</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>9327.68</v>
+        <v>7894.87</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>9333.32</v>
+        <v>8259.379999999999</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>8486.889999999999</v>
+        <v>8944.84</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -14548,80 +14309,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>321035.33</v>
+        <v>13326.19</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>321035.33</v>
+        <v>13326.19</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>334699.39</v>
+        <v>12648.92</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>354840.75</v>
+        <v>12775.08</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>331296.83</v>
+        <v>12429.39</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>337528.2</v>
+        <v>11620.34</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>337528.2</v>
+        <v>11620.34</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>333859.99</v>
+        <v>11502.21</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>332449.41</v>
+        <v>12054.79</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>324460.11</v>
+        <v>11954.55</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>314231.67</v>
+        <v>21317.29</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>314231.67</v>
+        <v>21317.29</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>331641.19</v>
+        <v>22023.49</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>323626.02</v>
+        <v>20964.84</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>307995.67</v>
+        <v>21523.47</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>296559.02</v>
+        <v>21557.75</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>296559.02</v>
+        <v>21557.75</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>272758.3</v>
+        <v>21483.76</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>257982.26</v>
+        <v>15376.15</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>257074.87</v>
+        <v>21335.78</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>235496.43</v>
+        <v>9327.68</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>235496.43</v>
+        <v>9327.68</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>225778.49</v>
+        <v>9333.32</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>225399.79</v>
+        <v>8486.889999999999</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -14643,80 +14404,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>165883.99</v>
+        <v>321035.33</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>165883.99</v>
+        <v>321035.33</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>168075.23</v>
+        <v>334699.39</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>172630.95</v>
+        <v>354840.75</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>174078.82</v>
+        <v>331296.83</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>170709.67</v>
+        <v>337528.2</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>170709.67</v>
+        <v>337528.2</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>169618.83</v>
+        <v>333859.99</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>167823.36</v>
+        <v>332449.41</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>157866.81</v>
+        <v>324460.11</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>194622.28</v>
+        <v>314231.67</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>194622.28</v>
+        <v>314231.67</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>196002.83</v>
+        <v>331641.19</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>195297.16</v>
+        <v>323626.02</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>192131.85</v>
+        <v>307995.67</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>186050.32</v>
+        <v>296559.02</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>186050.32</v>
+        <v>296559.02</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>186022.66</v>
+        <v>272758.3</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>161286.6</v>
+        <v>257982.26</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>143803.29</v>
+        <v>257074.87</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>135773.77</v>
+        <v>235496.43</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>135773.77</v>
+        <v>235496.43</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>136005.2</v>
+        <v>225778.49</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>137079.04</v>
+        <v>225399.79</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -14738,80 +14499,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>50655.19</v>
+        <v>165883.99</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>50655.19</v>
+        <v>165883.99</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>50655.19</v>
+        <v>168075.23</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>50655.19</v>
+        <v>172630.95</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>50655.19</v>
+        <v>174078.82</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>50655.19</v>
+        <v>170709.67</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>50655.19</v>
+        <v>170709.67</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>50655.19</v>
+        <v>169618.83</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>50655.19</v>
+        <v>167823.36</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>50655.19</v>
+        <v>157866.81</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>50655.19</v>
+        <v>194622.28</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>50655.19</v>
+        <v>194622.28</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>50655.19</v>
+        <v>196002.83</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>50655.19</v>
+        <v>195297.16</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>50655.19</v>
+        <v>192131.85</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>50655.19</v>
+        <v>186050.32</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>50655.19</v>
+        <v>186050.32</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>50655.19</v>
+        <v>186022.66</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>50655.19</v>
+        <v>161286.6</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>50655.19</v>
+        <v>143803.29</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>50655.19</v>
+        <v>135773.77</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>50655.19</v>
+        <v>135773.77</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>50655.19</v>
+        <v>136005.2</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>39051.76</v>
+        <v>137079.04</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -14833,80 +14594,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="K45" s="37" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="Y45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="Z45" s="37" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="AA45" s="18" t="n">
-        <v>94821.45</v>
+        <v>50655.19</v>
       </c>
       <c r="AB45" s="19" t="n">
-        <v>94821.45</v>
+        <v>39051.76</v>
       </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
@@ -14928,80 +14689,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>-77423.44</v>
+        <v>94821.45</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>-77423.44</v>
+        <v>94821.45</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>-74723.81</v>
+        <v>94821.45</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-74723.81</v>
+        <v>94821.45</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>-74723.81</v>
+        <v>94821.45</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>-74729.72</v>
+        <v>94821.45</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>-74729.72</v>
+        <v>94821.45</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>-74729.72</v>
+        <v>94821.45</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>-74501.11</v>
+        <v>94821.45</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>-83426.32000000001</v>
+        <v>94821.45</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>-87597</v>
+        <v>94821.45</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>-87597</v>
+        <v>94821.45</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>-87522.50999999999</v>
+        <v>94821.45</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>-88575.44</v>
+        <v>94821.45</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>-88575.44</v>
+        <v>94821.45</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>-84643.55</v>
+        <v>94821.45</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>-84643.55</v>
+        <v>94821.45</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>-84643.55</v>
+        <v>94821.45</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>-84643.55</v>
+        <v>94821.45</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>-84947.25999999999</v>
+        <v>94821.45</v>
       </c>
       <c r="Y46" s="18" t="n">
-        <v>-83592.16</v>
+        <v>94821.45</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>-83592.16</v>
+        <v>94821.45</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>-82661.50999999999</v>
+        <v>94821.45</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>-70019.77</v>
+        <v>94821.45</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -15023,80 +14784,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1454.45</v>
+        <v>-77423.44</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>1454.45</v>
+        <v>-77423.44</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1353.14</v>
+        <v>-74723.81</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>2063.54</v>
+        <v>-74723.81</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>2740.85</v>
+        <v>-74723.81</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>1257.95</v>
+        <v>-74729.72</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>1257.95</v>
+        <v>-74729.72</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>1631.35</v>
+        <v>-74729.72</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>1662.76</v>
+        <v>-74501.11</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>1391.88</v>
+        <v>-83426.32000000001</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>45822.47</v>
+        <v>-87597</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>45822.47</v>
+        <v>-87597</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>44720.79</v>
+        <v>-87522.50999999999</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>44972.59</v>
+        <v>-88575.44</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>44959.2</v>
+        <v>-88575.44</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>41978.19</v>
+        <v>-84643.55</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>41978.19</v>
+        <v>-84643.55</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>40897.29</v>
+        <v>-84643.55</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>40857.34</v>
+        <v>-84643.55</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>40816.92</v>
+        <v>-84947.25999999999</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>42005.92</v>
+        <v>-83592.16</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>42005.92</v>
+        <v>-83592.16</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>40893.68</v>
+        <v>-82661.50999999999</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>41195.83</v>
+        <v>-70019.77</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -15118,80 +14879,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>96376.35000000001</v>
+        <v>1454.45</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>96376.35000000001</v>
+        <v>1454.45</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>95969.25999999999</v>
+        <v>1353.14</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>99814.59</v>
+        <v>2063.54</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>100585.13</v>
+        <v>2740.85</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>98704.81</v>
+        <v>1257.95</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>98704.81</v>
+        <v>1257.95</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>97240.57000000001</v>
+        <v>1631.35</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>95185.07000000001</v>
+        <v>1662.76</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>94424.62</v>
+        <v>1391.88</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>90920.17999999999</v>
+        <v>45822.47</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>90920.17999999999</v>
+        <v>45822.47</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>93327.91</v>
+        <v>44720.79</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>93423.37</v>
+        <v>44972.59</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>90271.46000000001</v>
+        <v>44959.2</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>83239.03999999999</v>
+        <v>41978.19</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>83239.03999999999</v>
+        <v>41978.19</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>84292.28</v>
+        <v>40897.29</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>59596.16</v>
+        <v>40857.34</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>42457</v>
+        <v>40816.92</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>31883.37</v>
+        <v>42005.92</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>31883.37</v>
+        <v>42005.92</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>32296.4</v>
+        <v>40893.68</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>32029.77</v>
+        <v>41195.83</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -15213,80 +14974,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>비지배주주지분</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>32041.73</v>
+        <v>96376.35000000001</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>32041.73</v>
+        <v>96376.35000000001</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>28662.77</v>
+        <v>95969.25999999999</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>30372.03</v>
+        <v>99814.59</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>30805.91</v>
+        <v>100585.13</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>27446.62</v>
+        <v>98704.81</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>27446.62</v>
+        <v>98704.81</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>24738.86</v>
+        <v>97240.57000000001</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>22246.68</v>
+        <v>95185.07000000001</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>31901.02</v>
+        <v>94424.62</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>35248.88</v>
+        <v>90920.17999999999</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>35248.88</v>
+        <v>90920.17999999999</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>34495.95</v>
+        <v>93327.91</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>37104.96</v>
+        <v>93423.37</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>36021.68</v>
+        <v>90271.46000000001</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>30786.76</v>
+        <v>83239.03999999999</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>30786.76</v>
+        <v>83239.03999999999</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>30325.99</v>
+        <v>84292.28</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>30019.42</v>
+        <v>59596.16</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>29786.14</v>
+        <v>42457</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>28557.09</v>
+        <v>31883.37</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>28557.09</v>
+        <v>31883.37</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>27838.7</v>
+        <v>32296.4</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>28025.78</v>
+        <v>32029.77</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -15308,80 +15069,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>비지배주주지분</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>197925.73</v>
+        <v>32041.73</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>197925.73</v>
+        <v>32041.73</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>196738</v>
+        <v>28662.77</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>203002.98</v>
+        <v>30372.03</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>204884.72</v>
+        <v>30805.91</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>198156.3</v>
+        <v>27446.62</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>198156.3</v>
+        <v>27446.62</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>194357.69</v>
+        <v>24738.86</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>190070.04</v>
+        <v>22246.68</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>189767.84</v>
+        <v>31901.02</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>229871.16</v>
+        <v>35248.88</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>229871.16</v>
+        <v>35248.88</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>230498.78</v>
+        <v>34495.95</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>232402.12</v>
+        <v>37104.96</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>228153.53</v>
+        <v>36021.68</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>216837.08</v>
+        <v>30786.76</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>216837.08</v>
+        <v>30786.76</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>216348.65</v>
+        <v>30325.99</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>191306.02</v>
+        <v>30019.42</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>173589.43</v>
+        <v>29786.14</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>164330.86</v>
+        <v>28557.09</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>164330.86</v>
+        <v>28557.09</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>163843.91</v>
+        <v>27838.7</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>165104.81</v>
+        <v>28025.78</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -15403,80 +15164,80 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>518961.06</v>
+        <v>197925.73</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>518961.06</v>
+        <v>197925.73</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>531437.39</v>
+        <v>196738</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>557843.74</v>
+        <v>203002.98</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>536181.5600000001</v>
+        <v>204884.72</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>535684.5</v>
+        <v>198156.3</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>535684.5</v>
+        <v>198156.3</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>528217.6899999999</v>
+        <v>194357.69</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>522519.45</v>
+        <v>190070.04</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>514227.95</v>
+        <v>189767.84</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>544102.83</v>
+        <v>229871.16</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>544102.83</v>
+        <v>229871.16</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>562139.97</v>
+        <v>230498.78</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>556028.14</v>
+        <v>232402.12</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>536149.2</v>
+        <v>228153.53</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>513396.1</v>
+        <v>216837.08</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>513396.1</v>
+        <v>216837.08</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>489106.95</v>
+        <v>216348.65</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>449288.28</v>
+        <v>191306.02</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>430664.3</v>
+        <v>173589.43</v>
       </c>
       <c r="Y51" s="18" t="n">
-        <v>399827.28</v>
+        <v>164330.86</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>399827.28</v>
+        <v>164330.86</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>389622.4</v>
+        <v>163843.91</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>390504.61</v>
+        <v>165104.81</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -15498,80 +15259,80 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>222246.57</v>
+        <v>518961.06</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>222246.57</v>
+        <v>518961.06</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>228266.28</v>
+        <v>531437.39</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>250696.87</v>
+        <v>557843.74</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>240951.23</v>
+        <v>536181.5600000001</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>247619.33</v>
+        <v>535684.5</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>247619.33</v>
+        <v>535684.5</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>235104.04</v>
+        <v>528217.6899999999</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>235094.13</v>
+        <v>522519.45</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>212697.07</v>
+        <v>514227.95</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>208782.44</v>
+        <v>544102.83</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>208782.44</v>
+        <v>544102.83</v>
       </c>
       <c r="Q52" s="18" t="n">
-        <v>218135</v>
+        <v>562139.97</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>208377.12</v>
+        <v>556028.14</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>202355.39</v>
+        <v>536149.2</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>186390.43</v>
+        <v>513396.1</v>
       </c>
       <c r="U52" s="37" t="n">
-        <v>186390.43</v>
+        <v>513396.1</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>176581.45</v>
+        <v>489106.95</v>
       </c>
       <c r="W52" s="18" t="n">
-        <v>145194.23</v>
+        <v>449288.28</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>142430.59</v>
+        <v>430664.3</v>
       </c>
       <c r="Y52" s="18" t="n">
-        <v>135856.67</v>
+        <v>399827.28</v>
       </c>
       <c r="Z52" s="37" t="n">
-        <v>135856.67</v>
+        <v>399827.28</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>133943.07</v>
+        <v>389622.4</v>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>123354.72</v>
+        <v>390504.61</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -15593,80 +15354,80 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>210104.63</v>
+        <v>222246.57</v>
       </c>
       <c r="F53" s="37" t="n">
-        <v>210104.63</v>
+        <v>222246.57</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>214070.13</v>
+        <v>228266.28</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>230031.8</v>
+        <v>250696.87</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>229784.97</v>
+        <v>240951.23</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>229851.84</v>
+        <v>247619.33</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>229851.84</v>
+        <v>247619.33</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>227113.53</v>
+        <v>235104.04</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>222379.06</v>
+        <v>235094.13</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>200844.49</v>
+        <v>212697.07</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>198049.35</v>
+        <v>208782.44</v>
       </c>
       <c r="P53" s="37" t="n">
-        <v>198049.35</v>
+        <v>208782.44</v>
       </c>
       <c r="Q53" s="18" t="n">
-        <v>207134.41</v>
+        <v>218135</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>199877.46</v>
+        <v>208377.12</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>193635.57</v>
+        <v>202355.39</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>176438.23</v>
+        <v>186390.43</v>
       </c>
       <c r="U53" s="37" t="n">
-        <v>176438.23</v>
+        <v>186390.43</v>
       </c>
       <c r="V53" s="18" t="n">
-        <v>164277.89</v>
+        <v>176581.45</v>
       </c>
       <c r="W53" s="18" t="n">
-        <v>130807.78</v>
+        <v>145194.23</v>
       </c>
       <c r="X53" s="18" t="n">
-        <v>131231.26</v>
+        <v>142430.59</v>
       </c>
       <c r="Y53" s="18" t="n">
-        <v>124875.37</v>
+        <v>135856.67</v>
       </c>
       <c r="Z53" s="37" t="n">
-        <v>124875.37</v>
+        <v>135856.67</v>
       </c>
       <c r="AA53" s="18" t="n">
-        <v>125492.52</v>
+        <v>133943.07</v>
       </c>
       <c r="AB53" s="19" t="n">
-        <v>116464.98</v>
+        <v>123354.72</v>
       </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -15688,80 +15449,80 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
-        <v>14642.92</v>
+        <v>210104.63</v>
       </c>
       <c r="F54" s="37" t="n">
-        <v>14642.92</v>
+        <v>210104.63</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>16338</v>
+        <v>214070.13</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>23384.28</v>
+        <v>230031.8</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>13335.6</v>
+        <v>229784.97</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>19003.59</v>
+        <v>229851.84</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>19003.59</v>
+        <v>229851.84</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>9140.040000000001</v>
+        <v>227113.53</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>14011.75</v>
+        <v>222379.06</v>
       </c>
       <c r="N54" s="18" t="n">
-        <v>12773.77</v>
+        <v>200844.49</v>
       </c>
       <c r="O54" s="18" t="n">
-        <v>12367.84</v>
+        <v>198049.35</v>
       </c>
       <c r="P54" s="37" t="n">
-        <v>12367.84</v>
+        <v>198049.35</v>
       </c>
       <c r="Q54" s="18" t="n">
-        <v>11493.05</v>
+        <v>207134.41</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>9227.91</v>
+        <v>199877.46</v>
       </c>
       <c r="S54" s="18" t="n">
-        <v>9419.99</v>
+        <v>193635.57</v>
       </c>
       <c r="T54" s="18" t="n">
-        <v>10552.35</v>
+        <v>176438.23</v>
       </c>
       <c r="U54" s="37" t="n">
-        <v>10552.35</v>
+        <v>176438.23</v>
       </c>
       <c r="V54" s="18" t="n">
-        <v>12157.36</v>
+        <v>164277.89</v>
       </c>
       <c r="W54" s="18" t="n">
-        <v>14512.67</v>
+        <v>130807.78</v>
       </c>
       <c r="X54" s="18" t="n">
-        <v>11228.98</v>
+        <v>131231.26</v>
       </c>
       <c r="Y54" s="18" t="n">
-        <v>11020.75</v>
+        <v>124875.37</v>
       </c>
       <c r="Z54" s="37" t="n">
-        <v>11020.75</v>
+        <v>124875.37</v>
       </c>
       <c r="AA54" s="18" t="n">
-        <v>10241.86</v>
+        <v>125492.52</v>
       </c>
       <c r="AB54" s="19" t="n">
-        <v>9416.059999999999</v>
+        <v>116464.98</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -15783,66 +15544,80 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>매각예정비유동자산및처분자산</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>14642.92</v>
+      </c>
+      <c r="F55" s="37" t="n">
+        <v>14642.92</v>
+      </c>
+      <c r="G55" s="18" t="n">
+        <v>16338</v>
+      </c>
+      <c r="H55" s="18" t="n">
+        <v>23384.28</v>
+      </c>
       <c r="I55" s="18" t="n">
-        <v>2626.9</v>
+        <v>13335.6</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>2626.9</v>
+        <v>19003.59</v>
       </c>
       <c r="K55" s="37" t="n">
-        <v>2626.9</v>
+        <v>19003.59</v>
+      </c>
+      <c r="L55" s="18" t="n">
+        <v>9140.040000000001</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>4156.36</v>
+        <v>14011.75</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>4106.21</v>
+        <v>12773.77</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>22383.41</v>
+        <v>12367.84</v>
       </c>
       <c r="P55" s="37" t="n">
-        <v>22383.41</v>
+        <v>12367.84</v>
       </c>
       <c r="Q55" s="18" t="n">
-        <v>17434.8</v>
+        <v>11493.05</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>17434.8</v>
+        <v>9227.91</v>
       </c>
       <c r="S55" s="18" t="n">
-        <v>27878.69</v>
+        <v>9419.99</v>
       </c>
       <c r="T55" s="18" t="n">
-        <v>14698.12</v>
+        <v>10552.35</v>
       </c>
       <c r="U55" s="37" t="n">
-        <v>14698.12</v>
+        <v>10552.35</v>
       </c>
       <c r="V55" s="18" t="n">
-        <v>10756.11</v>
+        <v>12157.36</v>
       </c>
       <c r="W55" s="18" t="n">
-        <v>45254.01</v>
+        <v>14512.67</v>
       </c>
       <c r="X55" s="18" t="n">
-        <v>45254.01</v>
+        <v>11228.98</v>
       </c>
       <c r="Y55" s="18" t="n">
-        <v>67853.37</v>
+        <v>11020.75</v>
       </c>
       <c r="Z55" s="37" t="n">
-        <v>67853.37</v>
+        <v>11020.75</v>
       </c>
       <c r="AA55" s="18" t="n">
-        <v>57409.48</v>
+        <v>10241.86</v>
       </c>
       <c r="AB55" s="19" t="n">
-        <v>57409.48</v>
+        <v>9416.059999999999</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -15864,43 +15639,67 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>유동파생상품자산</t>
+          <t>매각예정비유동자산및처분자산</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
+      <c r="I56" s="18" t="n">
+        <v>2626.9</v>
+      </c>
       <c r="J56" s="18" t="n">
-        <v>459.39</v>
+        <v>2626.9</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>459.39</v>
-      </c>
-      <c r="L56" s="18" t="n">
-        <v>94.51000000000001</v>
+        <v>2626.9</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>62.65</v>
+        <v>4156.36</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>110.07</v>
+        <v>4106.21</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>39.44</v>
+        <v>22383.41</v>
       </c>
       <c r="P56" s="37" t="n">
-        <v>39.44</v>
+        <v>22383.41</v>
       </c>
       <c r="Q56" s="18" t="n">
-        <v>23.34</v>
+        <v>17434.8</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.39</v>
+        <v>17434.8</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="9" t="n"/>
-      <c r="Z56" s="9" t="n"/>
-      <c r="AB56" s="5" t="n"/>
+        <v>27878.69</v>
+      </c>
+      <c r="T56" s="18" t="n">
+        <v>14698.12</v>
+      </c>
+      <c r="U56" s="37" t="n">
+        <v>14698.12</v>
+      </c>
+      <c r="V56" s="18" t="n">
+        <v>10756.11</v>
+      </c>
+      <c r="W56" s="18" t="n">
+        <v>45254.01</v>
+      </c>
+      <c r="X56" s="18" t="n">
+        <v>45254.01</v>
+      </c>
+      <c r="Y56" s="18" t="n">
+        <v>67853.37</v>
+      </c>
+      <c r="Z56" s="37" t="n">
+        <v>67853.37</v>
+      </c>
+      <c r="AA56" s="18" t="n">
+        <v>57409.48</v>
+      </c>
+      <c r="AB56" s="19" t="n">
+        <v>57409.48</v>
+      </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
       <c r="AE56" s="11" t="n"/>
@@ -15921,7 +15720,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>단기금융자산</t>
+          <t>유동파생상품자산</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -15978,59 +15777,43 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>계약부채</t>
+          <t>단기금융자산</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="J58" s="18" t="n">
+        <v>459.39</v>
+      </c>
+      <c r="K58" s="37" t="n">
+        <v>459.39</v>
+      </c>
+      <c r="L58" s="18" t="n">
+        <v>94.51000000000001</v>
+      </c>
       <c r="M58" s="18" t="n">
-        <v>499.15</v>
+        <v>62.65</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>88.59</v>
+        <v>110.07</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>1023.79</v>
+        <v>39.44</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>1023.79</v>
+        <v>39.44</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>281.53</v>
+        <v>23.34</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>435.1</v>
+        <v>1.39</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>1043.4</v>
-      </c>
-      <c r="T58" s="18" t="n">
-        <v>880.67</v>
-      </c>
-      <c r="U58" s="37" t="n">
-        <v>880.67</v>
-      </c>
-      <c r="V58" s="18" t="n">
-        <v>204.88</v>
-      </c>
-      <c r="W58" s="18" t="n">
-        <v>147.7</v>
-      </c>
-      <c r="X58" s="18" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="Y58" s="18" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z58" s="37" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AA58" s="18" t="n">
-        <v>35.06</v>
-      </c>
-      <c r="AB58" s="19" t="n">
-        <v>101.36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U58" s="9" t="n"/>
+      <c r="Z58" s="9" t="n"/>
+      <c r="AB58" s="5" t="n"/>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
       <c r="AE58" s="11" t="n"/>
@@ -16051,32 +15834,58 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>계약부채</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="K59" s="9" t="n"/>
       <c r="M59" s="18" t="n">
-        <v>148524.7</v>
+        <v>499.15</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>152031.34</v>
+        <v>88.59</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>139635.63</v>
+        <v>1023.79</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>139635.63</v>
+        <v>1023.79</v>
+      </c>
+      <c r="Q59" s="18" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="R59" s="18" t="n">
+        <v>435.1</v>
+      </c>
+      <c r="S59" s="18" t="n">
+        <v>1043.4</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>143242.68</v>
+        <v>880.67</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>143242.68</v>
-      </c>
-      <c r="Z59" s="9" t="n"/>
+        <v>880.67</v>
+      </c>
+      <c r="V59" s="18" t="n">
+        <v>204.88</v>
+      </c>
+      <c r="W59" s="18" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="X59" s="18" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="Y59" s="18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Z59" s="37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AA59" s="18" t="n">
+        <v>35.06</v>
+      </c>
       <c r="AB59" s="19" t="n">
-        <v>97273.92999999999</v>
+        <v>101.36</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -16098,46 +15907,32 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="K60" s="9" t="n"/>
       <c r="M60" s="18" t="n">
-        <v>35700.62</v>
+        <v>148524.7</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>28203.59</v>
+        <v>152031.34</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>25039.89</v>
+        <v>139635.63</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>25039.89</v>
-      </c>
-      <c r="Q60" s="18" t="n">
-        <v>17992.86</v>
-      </c>
-      <c r="R60" s="18" t="n">
-        <v>10071.17</v>
-      </c>
-      <c r="S60" s="18" t="n">
-        <v>8200.360000000001</v>
+        <v>139635.63</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>7416.94</v>
+        <v>143242.68</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>7416.94</v>
-      </c>
-      <c r="Y60" s="18" t="n">
-        <v>2042.92</v>
-      </c>
-      <c r="Z60" s="37" t="n">
-        <v>2042.92</v>
-      </c>
+        <v>143242.68</v>
+      </c>
+      <c r="Z60" s="9" t="n"/>
       <c r="AB60" s="19" t="n">
-        <v>1399.23</v>
+        <v>97273.92999999999</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -16159,47 +15954,40 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="K61" s="9" t="n"/>
       <c r="M61" s="18" t="n">
-        <v>376.64</v>
+        <v>35700.62</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>565</v>
+        <v>28203.59</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>527.1900000000001</v>
+        <v>25039.89</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>527.1900000000001</v>
+        <v>25039.89</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>1028.71</v>
+        <v>17992.86</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>814.12</v>
+        <v>10071.17</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>686.25</v>
+        <v>8200.360000000001</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>651.5</v>
+        <v>7416.94</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>651.5</v>
-      </c>
-      <c r="Y61" s="18" t="n">
-        <v>1070.62</v>
-      </c>
-      <c r="Z61" s="37" t="n">
-        <v>1070.62</v>
-      </c>
-      <c r="AB61" s="19" t="n">
-        <v>389.48</v>
-      </c>
+        <v>7416.94</v>
+      </c>
+      <c r="Z61" s="9" t="n"/>
+      <c r="AB61" s="5" t="n"/>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
       <c r="AE61" s="11" t="n"/>
@@ -20829,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23197,28 +22985,28 @@
         </is>
       </c>
       <c r="E28" s="18" t="n">
-        <v>299.4</v>
+        <v>519.11</v>
       </c>
       <c r="F28" s="37" t="n">
-        <v>299.4</v>
+        <v>519.11</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>240.67</v>
+        <v>432.37</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>292.26</v>
+        <v>788.86</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>242.19</v>
+        <v>716.84</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>325.38</v>
+        <v>829.05</v>
       </c>
       <c r="K28" s="37" t="n">
-        <v>325.38</v>
+        <v>829.05</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>360.8</v>
+        <v>867.86</v>
       </c>
       <c r="M28" s="18" t="n">
         <v>671.21</v>
@@ -23762,80 +23550,80 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>6132.63</v>
+        <v>219.71</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>6132.63</v>
+        <v>219.71</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>6637.91</v>
+        <v>191.7</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>7171.06</v>
+        <v>496.6</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>7482.27</v>
+        <v>474.65</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>4775.05</v>
+        <v>503.67</v>
       </c>
       <c r="K35" s="37" t="n">
-        <v>4775.05</v>
+        <v>503.67</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>4739.98</v>
+        <v>507.06</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>4868.53</v>
+        <v>354.22</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>5146.41</v>
+        <v>560.4</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>5863.45</v>
+        <v>526.39</v>
       </c>
       <c r="P35" s="37" t="n">
-        <v>5863.45</v>
+        <v>526.39</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>2135.54</v>
+        <v>483.04</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>2423.84</v>
+        <v>483.54</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>2725.84</v>
+        <v>359.97</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>5638.04</v>
+        <v>321.04</v>
       </c>
       <c r="U35" s="37" t="n">
-        <v>5638.04</v>
+        <v>321.04</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>5441.07</v>
+        <v>292.37</v>
       </c>
       <c r="W35" s="18" t="n">
-        <v>5080.83</v>
+        <v>733.5599999999999</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>3778.42</v>
+        <v>747.88</v>
       </c>
       <c r="Y35" s="18" t="n">
-        <v>2474.33</v>
+        <v>732.7</v>
       </c>
       <c r="Z35" s="37" t="n">
-        <v>2474.33</v>
+        <v>732.7</v>
       </c>
       <c r="AA35" s="18" t="n">
-        <v>2186.12</v>
+        <v>156.84</v>
       </c>
       <c r="AB35" s="19" t="n">
-        <v>2339.13</v>
+        <v>125.1</v>
       </c>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
@@ -23857,80 +23645,80 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
-        <v>11116.36</v>
+        <v>219.71</v>
       </c>
       <c r="F36" s="37" t="n">
-        <v>11116.36</v>
+        <v>219.71</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>10576.49</v>
+        <v>1531.81</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>10840.04</v>
+        <v>496.6</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>10631.75</v>
+        <v>474.65</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>10029.25</v>
+        <v>503.67</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>10029.25</v>
+        <v>503.67</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>10048.51</v>
+        <v>507.06</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>10546.53</v>
+        <v>354.22</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>10528.54</v>
+        <v>560.4</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>20117.68</v>
+        <v>526.39</v>
       </c>
       <c r="P36" s="37" t="n">
-        <v>20117.68</v>
+        <v>526.39</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>20904.17</v>
+        <v>483.04</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>20265.25</v>
+        <v>483.54</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>20904.17</v>
+        <v>359.97</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>20983.01</v>
+        <v>321.04</v>
       </c>
       <c r="U36" s="37" t="n">
-        <v>20983.01</v>
+        <v>321.04</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>20983.01</v>
+        <v>292.37</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>14949.4</v>
+        <v>733.5599999999999</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>20983.01</v>
+        <v>747.88</v>
       </c>
       <c r="Y36" s="18" t="n">
-        <v>9048.91</v>
+        <v>2823.8</v>
       </c>
       <c r="Z36" s="37" t="n">
-        <v>9048.91</v>
+        <v>2823.8</v>
       </c>
       <c r="AA36" s="18" t="n">
-        <v>9048.91</v>
+        <v>1916.89</v>
       </c>
       <c r="AB36" s="19" t="n">
-        <v>8196.84</v>
+        <v>2110.56</v>
       </c>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
@@ -23952,80 +23740,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>173491.69</v>
+        <v>6132.63</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>173491.69</v>
+        <v>6132.63</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>209931.87</v>
+        <v>6637.91</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>187266.79</v>
+        <v>7171.06</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>192773.87</v>
+        <v>7482.27</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>177065.86</v>
+        <v>4775.05</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>177065.86</v>
+        <v>4775.05</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>174944.64</v>
+        <v>4739.98</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>171344.41</v>
+        <v>4868.53</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>162998.36</v>
+        <v>5146.41</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>165547.65</v>
+        <v>5863.45</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>165547.65</v>
+        <v>5863.45</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>135633.5</v>
+        <v>2135.54</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>129872.49</v>
+        <v>2423.84</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>125364.17</v>
+        <v>2725.84</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>128415.21</v>
+        <v>5638.04</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>128415.21</v>
+        <v>5638.04</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>112304.53</v>
+        <v>5441.07</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>100821.62</v>
+        <v>5080.83</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>101953.35</v>
+        <v>3778.42</v>
       </c>
       <c r="Y37" s="18" t="n">
-        <v>83205.39</v>
+        <v>2474.33</v>
       </c>
       <c r="Z37" s="37" t="n">
-        <v>83205.39</v>
+        <v>2474.33</v>
       </c>
       <c r="AA37" s="18" t="n">
-        <v>72168.74000000001</v>
+        <v>2186.12</v>
       </c>
       <c r="AB37" s="19" t="n">
-        <v>70909.85000000001</v>
+        <v>2339.13</v>
       </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
@@ -24047,80 +23835,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>50655.19</v>
+        <v>11116.36</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>50655.19</v>
+        <v>11116.36</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10576.49</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10840.04</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10631.75</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10029.25</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>50655.19</v>
+        <v>10029.25</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10048.51</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10546.53</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>50655.19</v>
+        <v>10528.54</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20117.68</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>50655.19</v>
+        <v>20117.68</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20904.17</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20265.25</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20904.17</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20983.01</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>50655.19</v>
+        <v>20983.01</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20983.01</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>50655.19</v>
+        <v>14949.4</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>50655.19</v>
+        <v>20983.01</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>50655.19</v>
+        <v>9048.91</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>50655.19</v>
+        <v>9048.91</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>50655.19</v>
+        <v>9048.91</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>39051.76</v>
+        <v>8196.84</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -24142,80 +23930,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>94821.45</v>
+        <v>173491.69</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>94821.45</v>
+        <v>173491.69</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>94821.45</v>
+        <v>209931.87</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>94821.45</v>
+        <v>187266.79</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>94821.45</v>
+        <v>192773.87</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>94821.45</v>
+        <v>177065.86</v>
       </c>
       <c r="K39" s="37" t="n">
-        <v>94821.45</v>
+        <v>177065.86</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>94821.45</v>
+        <v>174944.64</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>94821.45</v>
+        <v>171344.41</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>94821.45</v>
+        <v>162998.36</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>94821.45</v>
+        <v>165547.65</v>
       </c>
       <c r="P39" s="37" t="n">
-        <v>94821.45</v>
+        <v>165547.65</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>94821.45</v>
+        <v>135633.5</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>94821.45</v>
+        <v>129872.49</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>94821.45</v>
+        <v>125364.17</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>94821.45</v>
+        <v>128415.21</v>
       </c>
       <c r="U39" s="37" t="n">
-        <v>94821.45</v>
+        <v>128415.21</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>94821.45</v>
+        <v>112304.53</v>
       </c>
       <c r="W39" s="18" t="n">
-        <v>94821.45</v>
+        <v>100821.62</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>94821.45</v>
+        <v>101953.35</v>
       </c>
       <c r="Y39" s="18" t="n">
-        <v>94821.45</v>
+        <v>83205.39</v>
       </c>
       <c r="Z39" s="37" t="n">
-        <v>94821.45</v>
+        <v>83205.39</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>94821.45</v>
+        <v>72168.74000000001</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>94821.45</v>
+        <v>70909.85000000001</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -24237,80 +24025,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>-74141.44</v>
+        <v>50655.19</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>-74895.09</v>
+        <v>50655.19</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>-74920.67</v>
+        <v>50655.19</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>-73717.85000000001</v>
+        <v>50655.19</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>-73717.85000000001</v>
+        <v>50655.19</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>-72787.2</v>
+        <v>50655.19</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>-60145.46</v>
+        <v>39051.76</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -24332,80 +24120,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>4546.15</v>
+        <v>94821.45</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>4546.15</v>
+        <v>94821.45</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>7144.48</v>
+        <v>94821.45</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>7854.87</v>
+        <v>94821.45</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>8532.190000000001</v>
+        <v>94821.45</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>7043.37</v>
+        <v>94821.45</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>7043.37</v>
+        <v>94821.45</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>7416.77</v>
+        <v>94821.45</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>7587.32</v>
+        <v>94821.45</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>7779.01</v>
+        <v>94821.45</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>48757.41</v>
+        <v>94821.45</v>
       </c>
       <c r="P41" s="37" t="n">
-        <v>48757.41</v>
+        <v>94821.45</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>47655.73</v>
+        <v>94821.45</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>46854.59</v>
+        <v>94821.45</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>46841.2</v>
+        <v>94821.45</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>48735.4</v>
+        <v>94821.45</v>
       </c>
       <c r="U41" s="37" t="n">
-        <v>48735.4</v>
+        <v>94821.45</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>47554.68</v>
+        <v>94821.45</v>
       </c>
       <c r="W41" s="18" t="n">
-        <v>47542.6</v>
+        <v>94821.45</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>47502.18</v>
+        <v>94821.45</v>
       </c>
       <c r="Y41" s="18" t="n">
-        <v>48565.32</v>
+        <v>94821.45</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>48565.32</v>
+        <v>94821.45</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>47476.33</v>
+        <v>94821.45</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>47778.48</v>
+        <v>94821.45</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -24427,80 +24215,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>96376.35000000001</v>
+        <v>-74141.44</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>96376.35000000001</v>
+        <v>-74141.44</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>95969.25999999999</v>
+        <v>-74141.44</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>99814.59</v>
+        <v>-74141.44</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>100585.13</v>
+        <v>-74141.44</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>98704.81</v>
+        <v>-74141.44</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>98704.81</v>
+        <v>-74141.44</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>97240.57000000001</v>
+        <v>-74141.44</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>95185.07000000001</v>
+        <v>-74141.44</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>94412.03999999999</v>
+        <v>-74141.44</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>90920.17999999999</v>
+        <v>-74141.44</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>90920.17999999999</v>
+        <v>-74141.44</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>93327.91</v>
+        <v>-74895.09</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>93423.37</v>
+        <v>-74895.09</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>90271.46000000001</v>
+        <v>-74895.09</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>82295.72</v>
+        <v>-74895.09</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>82295.72</v>
+        <v>-74895.09</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>83376.84</v>
+        <v>-74895.09</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>58652.85</v>
+        <v>-74895.09</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>41506.53</v>
+        <v>-74920.67</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>30940.06</v>
+        <v>-73717.85000000001</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>30940.06</v>
+        <v>-73717.85000000001</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>31353.08</v>
+        <v>-72787.2</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>31086.45</v>
+        <v>-60145.46</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -24522,80 +24310,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>172257.7</v>
+        <v>4546.15</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>172257.7</v>
+        <v>4546.15</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>174448.94</v>
+        <v>7144.48</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>179004.66</v>
+        <v>7854.87</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>180452.52</v>
+        <v>8532.190000000001</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>177083.38</v>
+        <v>7043.37</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>177083.38</v>
+        <v>7043.37</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>175992.54</v>
+        <v>7416.77</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>174107.59</v>
+        <v>7587.32</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>173526.24</v>
+        <v>7779.01</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>211012.79</v>
+        <v>48757.41</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>211012.79</v>
+        <v>48757.41</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>211565.18</v>
+        <v>47655.73</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>210859.51</v>
+        <v>46854.59</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>207694.2</v>
+        <v>46841.2</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>201612.67</v>
+        <v>48735.4</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>201612.67</v>
+        <v>48735.4</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>201513.06</v>
+        <v>47554.68</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>176777</v>
+        <v>47542.6</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>159564.67</v>
+        <v>47502.18</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>151264.16</v>
+        <v>48565.32</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>151264.16</v>
+        <v>48565.32</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>151518.85</v>
+        <v>47476.33</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>152592.68</v>
+        <v>47778.48</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -24617,80 +24405,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>345749.39</v>
+        <v>96376.35000000001</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>345749.39</v>
+        <v>96376.35000000001</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>384380.8</v>
+        <v>95969.25999999999</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>366271.45</v>
+        <v>99814.59</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>373226.39</v>
+        <v>100585.13</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>354149.24</v>
+        <v>98704.81</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>354149.24</v>
+        <v>98704.81</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>350937.17</v>
+        <v>97240.57000000001</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>345452.01</v>
+        <v>95185.07000000001</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>336524.6</v>
+        <v>94412.03999999999</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>376560.43</v>
+        <v>90920.17999999999</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>376560.43</v>
+        <v>90920.17999999999</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>347198.68</v>
+        <v>93327.91</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>340732</v>
+        <v>93423.37</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>333058.38</v>
+        <v>90271.46000000001</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>330027.88</v>
+        <v>82295.72</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>330027.88</v>
+        <v>82295.72</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>313817.59</v>
+        <v>83376.84</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>277598.62</v>
+        <v>58652.85</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>261518.02</v>
+        <v>41506.53</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>234469.55</v>
+        <v>30940.06</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>234469.55</v>
+        <v>30940.06</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>223687.59</v>
+        <v>31353.08</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>223502.53</v>
+        <v>31086.45</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -24712,7 +24500,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
@@ -24807,80 +24595,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>123111.23</v>
+        <v>345749.39</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>123111.23</v>
+        <v>345749.39</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>133569.84</v>
+        <v>384380.8</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>135397.01</v>
+        <v>366271.45</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>137473.49</v>
+        <v>373226.39</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>134858.31</v>
+        <v>354149.24</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>134858.31</v>
+        <v>354149.24</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>128932.39</v>
+        <v>350937.17</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>127423.32</v>
+        <v>345452.01</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>116614.56</v>
+        <v>336524.6</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>106407.62</v>
+        <v>376560.43</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>106407.62</v>
+        <v>376560.43</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>88329.14</v>
+        <v>347198.68</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>81297.56</v>
+        <v>340732</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>76841.05</v>
+        <v>333058.38</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>75867.37</v>
+        <v>330027.88</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>75867.37</v>
+        <v>330027.88</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>67182.87</v>
+        <v>313817.59</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>51367.21</v>
+        <v>277598.62</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>47928.97</v>
+        <v>261518.02</v>
       </c>
       <c r="Y46" s="18" t="n">
-        <v>44448.39</v>
+        <v>234469.55</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>44448.39</v>
+        <v>234469.55</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>41196.26</v>
+        <v>223687.59</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>38761.32</v>
+        <v>223502.53</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -24902,80 +24690,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>119750.66</v>
+        <v>172257.7</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>119750.66</v>
+        <v>172257.7</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>126557.61</v>
+        <v>174448.94</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>129709.26</v>
+        <v>179004.66</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>134121.86</v>
+        <v>180452.52</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>127987.2</v>
+        <v>177083.38</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>127987.2</v>
+        <v>177083.38</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>124071.63</v>
+        <v>175992.54</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>118984.8</v>
+        <v>174107.59</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>109847.61</v>
+        <v>173526.24</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>99761.63</v>
+        <v>211012.79</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>99761.63</v>
+        <v>211012.79</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>81889.87</v>
+        <v>211565.18</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>77820.00999999999</v>
+        <v>210859.51</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>74409.95</v>
+        <v>207694.2</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>70417.74000000001</v>
+        <v>201612.67</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>70417.74000000001</v>
+        <v>201612.67</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>58625.23</v>
+        <v>201513.06</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>44808.59</v>
+        <v>176777</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>41662.78</v>
+        <v>159564.67</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>37648.93</v>
+        <v>151264.16</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>37648.93</v>
+        <v>151264.16</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>37736.15</v>
+        <v>151518.85</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>35976.13</v>
+        <v>152592.68</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -24997,80 +24785,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>5030.55</v>
+        <v>123111.23</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>5030.55</v>
+        <v>123111.23</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>8320.08</v>
+        <v>133569.84</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>7239.96</v>
+        <v>135397.01</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>4350.97</v>
+        <v>137473.49</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>7924.21</v>
+        <v>134858.31</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>7924.21</v>
+        <v>134858.31</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>5824.29</v>
+        <v>128932.39</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>9546.200000000001</v>
+        <v>127423.32</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>7684.14</v>
+        <v>116614.56</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>8278.74</v>
+        <v>106407.62</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>8278.74</v>
+        <v>106407.62</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>6914.4</v>
+        <v>88329.14</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>4187.91</v>
+        <v>81297.56</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>3112.07</v>
+        <v>76841.05</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>6026.08</v>
+        <v>75867.37</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>6026.08</v>
+        <v>75867.37</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>8384.16</v>
+        <v>67182.87</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>6655.67</v>
+        <v>51367.21</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>6263.23</v>
+        <v>47928.97</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>6802.96</v>
+        <v>44448.39</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>6802.96</v>
+        <v>44448.39</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>5211.13</v>
+        <v>41196.26</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>2788.69</v>
+        <v>38761.32</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -25092,27 +24880,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>사채</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="n"/>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>119750.66</v>
+      </c>
+      <c r="F49" s="37" t="n">
+        <v>119750.66</v>
+      </c>
       <c r="G49" s="18" t="n">
-        <v>6083.08</v>
-      </c>
-      <c r="K49" s="9" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="U49" s="9" t="n"/>
+        <v>126557.61</v>
+      </c>
+      <c r="H49" s="18" t="n">
+        <v>129709.26</v>
+      </c>
+      <c r="I49" s="18" t="n">
+        <v>134121.86</v>
+      </c>
+      <c r="J49" s="18" t="n">
+        <v>127987.2</v>
+      </c>
+      <c r="K49" s="37" t="n">
+        <v>127987.2</v>
+      </c>
+      <c r="L49" s="18" t="n">
+        <v>124071.63</v>
+      </c>
+      <c r="M49" s="18" t="n">
+        <v>118984.8</v>
+      </c>
+      <c r="N49" s="18" t="n">
+        <v>109847.61</v>
+      </c>
+      <c r="O49" s="18" t="n">
+        <v>99761.63</v>
+      </c>
+      <c r="P49" s="37" t="n">
+        <v>99761.63</v>
+      </c>
+      <c r="Q49" s="18" t="n">
+        <v>81889.87</v>
+      </c>
+      <c r="R49" s="18" t="n">
+        <v>77820.00999999999</v>
+      </c>
+      <c r="S49" s="18" t="n">
+        <v>74409.95</v>
+      </c>
+      <c r="T49" s="18" t="n">
+        <v>70417.74000000001</v>
+      </c>
+      <c r="U49" s="37" t="n">
+        <v>70417.74000000001</v>
+      </c>
+      <c r="V49" s="18" t="n">
+        <v>58625.23</v>
+      </c>
+      <c r="W49" s="18" t="n">
+        <v>44808.59</v>
+      </c>
+      <c r="X49" s="18" t="n">
+        <v>41662.78</v>
+      </c>
       <c r="Y49" s="18" t="n">
-        <v>2594.46</v>
+        <v>37648.93</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>2594.46</v>
+        <v>37648.93</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>2184.36</v>
+        <v>37736.15</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>2281.56</v>
+        <v>35976.13</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -25134,27 +24975,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>장기파생상품부채</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>5030.55</v>
+      </c>
+      <c r="F50" s="37" t="n">
+        <v>5030.55</v>
+      </c>
       <c r="G50" s="18" t="n">
-        <v>1340.11</v>
-      </c>
-      <c r="K50" s="9" t="n"/>
-      <c r="P50" s="9" t="n"/>
-      <c r="U50" s="9" t="n"/>
+        <v>8320.08</v>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>7239.96</v>
+      </c>
+      <c r="I50" s="18" t="n">
+        <v>4350.97</v>
+      </c>
+      <c r="J50" s="18" t="n">
+        <v>7924.21</v>
+      </c>
+      <c r="K50" s="37" t="n">
+        <v>7924.21</v>
+      </c>
+      <c r="L50" s="18" t="n">
+        <v>5824.29</v>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>9546.200000000001</v>
+      </c>
+      <c r="N50" s="18" t="n">
+        <v>7684.14</v>
+      </c>
+      <c r="O50" s="18" t="n">
+        <v>8278.74</v>
+      </c>
+      <c r="P50" s="37" t="n">
+        <v>8278.74</v>
+      </c>
+      <c r="Q50" s="18" t="n">
+        <v>6914.4</v>
+      </c>
+      <c r="R50" s="18" t="n">
+        <v>4187.91</v>
+      </c>
+      <c r="S50" s="18" t="n">
+        <v>3112.07</v>
+      </c>
+      <c r="T50" s="18" t="n">
+        <v>6026.08</v>
+      </c>
+      <c r="U50" s="37" t="n">
+        <v>6026.08</v>
+      </c>
+      <c r="V50" s="18" t="n">
+        <v>8384.16</v>
+      </c>
+      <c r="W50" s="18" t="n">
+        <v>6655.67</v>
+      </c>
+      <c r="X50" s="18" t="n">
+        <v>6263.23</v>
+      </c>
       <c r="Y50" s="18" t="n">
-        <v>2091.1</v>
+        <v>6802.96</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>2091.1</v>
+        <v>6802.96</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>1760.05</v>
+        <v>5211.13</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>1985.46</v>
+        <v>2788.69</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -25176,61 +25070,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>사채</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
       <c r="G51" s="18" t="n">
-        <v>1340.11</v>
+        <v>6083.08</v>
       </c>
       <c r="K51" s="9" t="n"/>
-      <c r="M51" s="18" t="n">
-        <v>354.22</v>
-      </c>
-      <c r="N51" s="18" t="n">
-        <v>560.4</v>
-      </c>
-      <c r="O51" s="18" t="n">
-        <v>526.39</v>
-      </c>
-      <c r="P51" s="37" t="n">
-        <v>526.39</v>
-      </c>
-      <c r="Q51" s="18" t="n">
-        <v>483.04</v>
-      </c>
-      <c r="R51" s="18" t="n">
-        <v>483.54</v>
-      </c>
-      <c r="S51" s="18" t="n">
-        <v>359.97</v>
-      </c>
-      <c r="T51" s="18" t="n">
-        <v>321.04</v>
-      </c>
-      <c r="U51" s="37" t="n">
-        <v>321.04</v>
-      </c>
-      <c r="V51" s="18" t="n">
-        <v>292.37</v>
-      </c>
-      <c r="W51" s="18" t="n">
-        <v>733.5599999999999</v>
-      </c>
-      <c r="X51" s="18" t="n">
-        <v>747.88</v>
-      </c>
+      <c r="P51" s="9" t="n"/>
+      <c r="U51" s="9" t="n"/>
       <c r="Y51" s="18" t="n">
-        <v>2823.8</v>
+        <v>2594.46</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>2823.8</v>
+        <v>2594.46</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>1916.89</v>
+        <v>2184.36</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>2110.56</v>
+        <v>2281.56</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -25252,54 +25112,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>매각예정비유동자산및처분자산</t>
+          <t>장기파생상품부채</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
-      <c r="I52" s="18" t="n">
-        <v>2626.9</v>
-      </c>
-      <c r="J52" s="18" t="n">
-        <v>2626.9</v>
-      </c>
-      <c r="K52" s="37" t="n">
-        <v>2626.9</v>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>6105.86</v>
-      </c>
-      <c r="N52" s="18" t="n">
-        <v>6034.71</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>5827.81</v>
-      </c>
-      <c r="P52" s="37" t="n">
-        <v>5827.81</v>
-      </c>
-      <c r="S52" s="18" t="n">
-        <v>10443.89</v>
-      </c>
-      <c r="T52" s="18" t="n">
-        <v>14150.1</v>
-      </c>
-      <c r="U52" s="37" t="n">
-        <v>14150.1</v>
-      </c>
-      <c r="V52" s="18" t="n">
-        <v>10443.89</v>
-      </c>
-      <c r="W52" s="18" t="n">
-        <v>44941.79</v>
-      </c>
-      <c r="X52" s="18" t="n">
-        <v>44941.79</v>
-      </c>
-      <c r="Z52" s="9" t="n"/>
+      <c r="G52" s="18" t="n">
+        <v>1340.11</v>
+      </c>
+      <c r="K52" s="9" t="n"/>
+      <c r="P52" s="9" t="n"/>
+      <c r="U52" s="9" t="n"/>
+      <c r="Y52" s="18" t="n">
+        <v>2091.1</v>
+      </c>
+      <c r="Z52" s="37" t="n">
+        <v>2091.1</v>
+      </c>
       <c r="AA52" s="18" t="n">
-        <v>57409.48</v>
-      </c>
-      <c r="AB52" s="5" t="n"/>
+        <v>1760.05</v>
+      </c>
+      <c r="AB52" s="19" t="n">
+        <v>1985.46</v>
+      </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
       <c r="AE52" s="11" t="n"/>
@@ -25320,25 +25154,53 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>유동파생상품자산</t>
+          <t>매각예정비유동자산및처분자산</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
+      <c r="I53" s="18" t="n">
+        <v>2626.9</v>
+      </c>
       <c r="J53" s="18" t="n">
-        <v>25.71</v>
+        <v>2626.9</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="L53" s="18" t="n">
-        <v>15.13</v>
+        <v>2626.9</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="P53" s="9" t="n"/>
-      <c r="U53" s="9" t="n"/>
+        <v>6105.86</v>
+      </c>
+      <c r="N53" s="18" t="n">
+        <v>6034.71</v>
+      </c>
+      <c r="O53" s="18" t="n">
+        <v>5827.81</v>
+      </c>
+      <c r="P53" s="37" t="n">
+        <v>5827.81</v>
+      </c>
+      <c r="S53" s="18" t="n">
+        <v>10443.89</v>
+      </c>
+      <c r="T53" s="18" t="n">
+        <v>14150.1</v>
+      </c>
+      <c r="U53" s="37" t="n">
+        <v>14150.1</v>
+      </c>
+      <c r="V53" s="18" t="n">
+        <v>10443.89</v>
+      </c>
+      <c r="W53" s="18" t="n">
+        <v>44941.79</v>
+      </c>
+      <c r="X53" s="18" t="n">
+        <v>44941.79</v>
+      </c>
       <c r="Z53" s="9" t="n"/>
+      <c r="AA53" s="18" t="n">
+        <v>57409.48</v>
+      </c>
       <c r="AB53" s="5" t="n"/>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -25360,7 +25222,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>단기금융자산</t>
+          <t>유동파생상품자산</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -25400,47 +25262,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>계약부채</t>
+          <t>단기금융자산</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
+      <c r="J55" s="18" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="K55" s="37" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="L55" s="18" t="n">
+        <v>15.13</v>
+      </c>
       <c r="M55" s="18" t="n">
-        <v>499.15</v>
-      </c>
-      <c r="N55" s="18" t="n">
-        <v>88.59</v>
-      </c>
-      <c r="O55" s="18" t="n">
-        <v>104.17</v>
-      </c>
-      <c r="P55" s="37" t="n">
-        <v>104.17</v>
-      </c>
-      <c r="Q55" s="18" t="n">
-        <v>237.37</v>
-      </c>
-      <c r="R55" s="18" t="n">
-        <v>419.02</v>
-      </c>
-      <c r="S55" s="18" t="n">
-        <v>1009.91</v>
-      </c>
-      <c r="T55" s="18" t="n">
-        <v>847.89</v>
-      </c>
-      <c r="U55" s="37" t="n">
-        <v>847.89</v>
-      </c>
-      <c r="V55" s="18" t="n">
-        <v>158.87</v>
-      </c>
-      <c r="W55" s="18" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="X55" s="18" t="n">
-        <v>0</v>
-      </c>
+        <v>6.98</v>
+      </c>
+      <c r="P55" s="9" t="n"/>
+      <c r="U55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AB55" s="5" t="n"/>
       <c r="AC55" s="10" t="n"/>
@@ -25463,59 +25302,49 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>계약부채</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
       <c r="K56" s="9" t="n"/>
       <c r="M56" s="18" t="n">
-        <v>96758.42</v>
+        <v>499.15</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>96768.67999999999</v>
+        <v>88.59</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>90823.85000000001</v>
+        <v>104.17</v>
       </c>
       <c r="P56" s="37" t="n">
-        <v>90823.85000000001</v>
+        <v>104.17</v>
       </c>
       <c r="Q56" s="18" t="n">
-        <v>79509.35000000001</v>
+        <v>237.37</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>76160.89</v>
+        <v>419.02</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>74341.05</v>
+        <v>1009.91</v>
       </c>
       <c r="T56" s="18" t="n">
-        <v>74617.37</v>
+        <v>847.89</v>
       </c>
       <c r="U56" s="37" t="n">
-        <v>74617.37</v>
+        <v>847.89</v>
       </c>
       <c r="V56" s="18" t="n">
-        <v>67182.87</v>
+        <v>158.87</v>
       </c>
       <c r="W56" s="18" t="n">
-        <v>51367.21</v>
+        <v>132.5</v>
       </c>
       <c r="X56" s="18" t="n">
-        <v>47928.97</v>
-      </c>
-      <c r="Y56" s="18" t="n">
-        <v>41853.93</v>
-      </c>
-      <c r="Z56" s="37" t="n">
-        <v>41853.93</v>
-      </c>
-      <c r="AA56" s="18" t="n">
-        <v>39011.9</v>
-      </c>
-      <c r="AB56" s="19" t="n">
-        <v>36479.76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z56" s="9" t="n"/>
+      <c r="AB56" s="5" t="n"/>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
       <c r="AE56" s="11" t="n"/>
@@ -25536,40 +25365,59 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
       <c r="K57" s="9" t="n"/>
       <c r="M57" s="18" t="n">
-        <v>16199.35</v>
+        <v>96758.42</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>14005.91</v>
+        <v>96768.67999999999</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>11812.46</v>
+        <v>90823.85000000001</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>11812.46</v>
+        <v>90823.85000000001</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>5833.33</v>
+        <v>79509.35000000001</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>4166.67</v>
+        <v>76160.89</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>2500</v>
+        <v>74341.05</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>1250</v>
+        <v>74617.37</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Z57" s="9" t="n"/>
-      <c r="AB57" s="5" t="n"/>
+        <v>74617.37</v>
+      </c>
+      <c r="V57" s="18" t="n">
+        <v>67182.87</v>
+      </c>
+      <c r="W57" s="18" t="n">
+        <v>51367.21</v>
+      </c>
+      <c r="X57" s="18" t="n">
+        <v>47928.97</v>
+      </c>
+      <c r="Y57" s="18" t="n">
+        <v>41853.93</v>
+      </c>
+      <c r="Z57" s="37" t="n">
+        <v>41853.93</v>
+      </c>
+      <c r="AA57" s="18" t="n">
+        <v>39011.9</v>
+      </c>
+      <c r="AB57" s="19" t="n">
+        <v>36479.76</v>
+      </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
       <c r="AE57" s="11" t="n"/>
@@ -25590,59 +25438,40 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
       <c r="M58" s="18" t="n">
-        <v>354.22</v>
+        <v>16199.35</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>560.4</v>
+        <v>14005.91</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>526.39</v>
+        <v>11812.46</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>526.39</v>
+        <v>11812.46</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>483.04</v>
+        <v>5833.33</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>483.54</v>
+        <v>4166.67</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>359.97</v>
+        <v>2500</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>321.04</v>
+        <v>1250</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>321.04</v>
-      </c>
-      <c r="V58" s="18" t="n">
-        <v>292.37</v>
-      </c>
-      <c r="W58" s="18" t="n">
-        <v>733.5599999999999</v>
-      </c>
-      <c r="X58" s="18" t="n">
-        <v>747.88</v>
-      </c>
-      <c r="Y58" s="18" t="n">
-        <v>732.7</v>
-      </c>
-      <c r="Z58" s="37" t="n">
-        <v>732.7</v>
-      </c>
-      <c r="AA58" s="18" t="n">
-        <v>156.84</v>
-      </c>
-      <c r="AB58" s="19" t="n">
-        <v>125.1</v>
-      </c>
+        <v>1250</v>
+      </c>
+      <c r="Z58" s="9" t="n"/>
+      <c r="AB58" s="5" t="n"/>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
       <c r="AE58" s="11" t="n"/>
@@ -30530,11 +30359,11 @@
         <v/>
       </c>
       <c r="AC12" s="20">
-        <f>IFERROR((AB29*변수!$D$56-AB27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AB29*변수!$D$55-AB27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC29*변수!$D$56-AC27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AC29*변수!$D$55-AC27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -30542,19 +30371,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD29*변수!$D$56-AD27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AD29*변수!$D$55-AD27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF29*변수!$D$56-AF27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AF29*변수!$D$55-AF27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG29*변수!$D$56-AG27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AG29*변수!$D$55-AG27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH29*변수!$D$56-AH27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AH29*변수!$D$55-AH27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -30562,19 +30391,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI29*변수!$D$56-AI27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AI29*변수!$D$55-AI27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK29*변수!$D$56-AK27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AK29*변수!$D$55-AK27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL29*변수!$D$56-AL27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AL29*변수!$D$55-AL27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM29*변수!$D$56-AM27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AM29*변수!$D$55-AM27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -33745,79 +33574,79 @@
           <t>유통주식수</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
-        <v>69.502</v>
+      <c r="E33" s="32" t="n">
+        <v>13.9003692</v>
       </c>
       <c r="F33" s="28">
         <f>E33</f>
         <v/>
       </c>
-      <c r="G33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>69.502</v>
+      <c r="G33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="H33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="I33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="J33" s="32" t="n">
+        <v>13.9003692</v>
       </c>
       <c r="K33" s="28">
         <f>J33</f>
         <v/>
       </c>
-      <c r="L33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="N33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="O33" s="27" t="n">
-        <v>69.502</v>
+      <c r="L33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="M33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="N33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="O33" s="32" t="n">
+        <v>13.9003692</v>
       </c>
       <c r="P33" s="28">
         <f>O33</f>
         <v/>
       </c>
-      <c r="Q33" s="27" t="n">
-        <v>69.502</v>
-      </c>
-      <c r="R33" s="27" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="S33" s="27" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="T33" s="27" t="n">
-        <v>68.17</v>
+      <c r="Q33" s="32" t="n">
+        <v>13.9003692</v>
+      </c>
+      <c r="R33" s="32" t="n">
+        <v>13.6340606</v>
+      </c>
+      <c r="S33" s="32" t="n">
+        <v>13.6340606</v>
+      </c>
+      <c r="T33" s="32" t="n">
+        <v>13.6340606</v>
       </c>
       <c r="U33" s="28">
         <f>T33</f>
         <v/>
       </c>
-      <c r="V33" s="27" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="W33" s="27" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="X33" s="27" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="Y33" s="27" t="n">
-        <v>68.104</v>
+      <c r="V33" s="32" t="n">
+        <v>13.6340606</v>
+      </c>
+      <c r="W33" s="32" t="n">
+        <v>13.6340606</v>
+      </c>
+      <c r="X33" s="32" t="n">
+        <v>13.6340606</v>
+      </c>
+      <c r="Y33" s="32" t="n">
+        <v>13.6207034</v>
       </c>
       <c r="Z33" s="28">
         <f>Y33</f>
         <v/>
       </c>
-      <c r="AA33" s="27" t="n">
-        <v>68.104</v>
+      <c r="AA33" s="32" t="n">
+        <v>13.6207034</v>
       </c>
       <c r="AB33" s="29" t="n">
         <v>14.008</v>
@@ -34063,86 +33892,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E35" s="18" t="n">
-        <v>48.5</v>
+      <c r="E35" s="18">
+        <f>IFERROR(E34,"")</f>
+        <v/>
       </c>
       <c r="F35" s="37" t="n"/>
-      <c r="G35" s="18" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="H35" s="18" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="I35" s="18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J35" s="18" t="n">
-        <v>-66.3</v>
+      <c r="G35" s="18">
+        <f>IFERROR(G34,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IFERROR(H34,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="18">
+        <f>IFERROR(I34,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="18">
+        <f>IFERROR(J34,"")</f>
+        <v/>
       </c>
       <c r="K35" s="37">
         <f>SUM(G35:J35)</f>
         <v/>
       </c>
-      <c r="L35" s="18" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="M35" s="18" t="n">
-        <v>-29.2</v>
-      </c>
-      <c r="N35" s="18" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="O35" s="18" t="n">
-        <v>-31.3</v>
+      <c r="L35" s="18">
+        <f>IFERROR(L34,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="18">
+        <f>IFERROR(M34,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="18">
+        <f>IFERROR(N34,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="18">
+        <f>IFERROR(O34,"")</f>
+        <v/>
       </c>
       <c r="P35" s="37">
         <f>SUM(L35:O35)</f>
         <v/>
       </c>
-      <c r="Q35" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="R35" s="18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S35" s="18" t="n">
-        <v>-46</v>
-      </c>
-      <c r="T35" s="18" t="n">
-        <v>-106.2</v>
+      <c r="Q35" s="18">
+        <f>IFERROR(Q34,"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="18">
+        <f>IFERROR(R34,"")</f>
+        <v/>
+      </c>
+      <c r="S35" s="18">
+        <f>IFERROR(S34,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="18">
+        <f>IFERROR(T34,"")</f>
+        <v/>
       </c>
       <c r="U35" s="37">
         <f>SUM(Q35:T35)</f>
         <v/>
       </c>
-      <c r="V35" s="18" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="W35" s="18" t="n">
-        <v>-361.9</v>
-      </c>
-      <c r="X35" s="18" t="n">
-        <v>-251.3</v>
-      </c>
-      <c r="Y35" s="20" t="n">
-        <v>44.4</v>
+      <c r="V35" s="18">
+        <f>IFERROR(V34,"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="18">
+        <f>IFERROR(W34,"")</f>
+        <v/>
+      </c>
+      <c r="X35" s="18">
+        <f>IFERROR(X34,"")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="20">
+        <f>IFERROR((Y21-(-156.9)*(0.9315))*100/Y33,"")</f>
+        <v/>
       </c>
       <c r="Z35" s="37">
         <f>SUM(V35:Y35)</f>
         <v/>
       </c>
-      <c r="AA35" s="18" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="AB35" s="19" t="n">
-        <v>2.9</v>
+      <c r="AA35" s="18">
+        <f>IFERROR(AA34,"")</f>
+        <v/>
+      </c>
+      <c r="AB35" s="19">
+        <f>IFERROR(AB34,"")</f>
+        <v/>
       </c>
       <c r="AC35" s="20">
-        <f>IFERROR(X35*(1+변수!AC42),"")</f>
+        <f>IFERROR(AC34,"")</f>
         <v/>
       </c>
       <c r="AD35" s="20">
-        <f>IFERROR(Y35*(1+변수!AD42),"")</f>
+        <f>IFERROR(AD34,"")</f>
         <v/>
       </c>
       <c r="AE35" s="38">
@@ -34150,19 +33998,19 @@
         <v/>
       </c>
       <c r="AF35" s="20">
-        <f>IFERROR(AA35*(1+변수!AF42),"")</f>
+        <f>IFERROR(AF34,"")</f>
         <v/>
       </c>
       <c r="AG35" s="20">
-        <f>IFERROR(AB35*(1+변수!AG42),"")</f>
+        <f>IFERROR(AG34,"")</f>
         <v/>
       </c>
       <c r="AH35" s="20">
-        <f>IFERROR(AC35*(1+변수!AH42),"")</f>
+        <f>IFERROR(AH34,"")</f>
         <v/>
       </c>
       <c r="AI35" s="20">
-        <f>IFERROR(AD35*(1+변수!AI42),"")</f>
+        <f>IFERROR(AI34,"")</f>
         <v/>
       </c>
       <c r="AJ35" s="38">
@@ -34170,19 +34018,19 @@
         <v/>
       </c>
       <c r="AK35" s="20">
-        <f>IFERROR(AF35*(1+변수!AK42),"")</f>
+        <f>IFERROR(AK34,"")</f>
         <v/>
       </c>
       <c r="AL35" s="20">
-        <f>IFERROR(AG35*(1+변수!AL42),"")</f>
+        <f>IFERROR(AL34,"")</f>
         <v/>
       </c>
       <c r="AM35" s="20">
-        <f>IFERROR(AH35*(1+변수!AM42),"")</f>
+        <f>IFERROR(AM34,"")</f>
         <v/>
       </c>
       <c r="AN35" s="20">
-        <f>IFERROR(AI35*(1+변수!AN42),"")</f>
+        <f>IFERROR(AN34,"")</f>
         <v/>
       </c>
       <c r="AO35" s="38">
@@ -34431,7 +34279,7 @@
       <c r="AB37" s="19" t="n"/>
       <c r="AC37" s="20" t="n"/>
       <c r="AD37" s="20">
-        <f>변수!AD43</f>
+        <f>변수!AD42</f>
         <v/>
       </c>
       <c r="AE37" s="38">
@@ -34442,7 +34290,7 @@
       <c r="AG37" s="20" t="n"/>
       <c r="AH37" s="20" t="n"/>
       <c r="AI37" s="20">
-        <f>변수!AI43</f>
+        <f>변수!AI42</f>
         <v/>
       </c>
       <c r="AJ37" s="38">
@@ -34453,7 +34301,7 @@
       <c r="AL37" s="20" t="n"/>
       <c r="AM37" s="20" t="n"/>
       <c r="AN37" s="20">
-        <f>변수!AN43</f>
+        <f>변수!AN42</f>
         <v/>
       </c>
       <c r="AO37" s="38">
@@ -34665,11 +34513,11 @@
         <v/>
       </c>
       <c r="AC39" s="39">
-        <f>IFERROR(변수!$D$46/AC36,"")</f>
+        <f>IFERROR(변수!$D$45/AC36,"")</f>
         <v/>
       </c>
       <c r="AD39" s="39">
-        <f>IFERROR(변수!$D$46/AD36,"")</f>
+        <f>IFERROR(변수!$D$45/AD36,"")</f>
         <v/>
       </c>
       <c r="AE39" s="40">
@@ -34677,19 +34525,19 @@
         <v/>
       </c>
       <c r="AF39" s="39">
-        <f>IFERROR(변수!$D$46/AF36,"")</f>
+        <f>IFERROR(변수!$D$45/AF36,"")</f>
         <v/>
       </c>
       <c r="AG39" s="39">
-        <f>IFERROR(변수!$D$46/AG36,"")</f>
+        <f>IFERROR(변수!$D$45/AG36,"")</f>
         <v/>
       </c>
       <c r="AH39" s="39">
-        <f>IFERROR(변수!$D$46/AH36,"")</f>
+        <f>IFERROR(변수!$D$45/AH36,"")</f>
         <v/>
       </c>
       <c r="AI39" s="39">
-        <f>IFERROR(변수!$D$46/AI36,"")</f>
+        <f>IFERROR(변수!$D$45/AI36,"")</f>
         <v/>
       </c>
       <c r="AJ39" s="40">
@@ -34697,19 +34545,19 @@
         <v/>
       </c>
       <c r="AK39" s="39">
-        <f>IFERROR(변수!$D$46/AK36,"")</f>
+        <f>IFERROR(변수!$D$45/AK36,"")</f>
         <v/>
       </c>
       <c r="AL39" s="39">
-        <f>IFERROR(변수!$D$46/AL36,"")</f>
+        <f>IFERROR(변수!$D$45/AL36,"")</f>
         <v/>
       </c>
       <c r="AM39" s="39">
-        <f>IFERROR(변수!$D$46/AM36,"")</f>
+        <f>IFERROR(변수!$D$45/AM36,"")</f>
         <v/>
       </c>
       <c r="AN39" s="39">
-        <f>IFERROR(변수!$D$46/AN36,"")</f>
+        <f>IFERROR(변수!$D$45/AN36,"")</f>
         <v/>
       </c>
       <c r="AO39" s="40">
@@ -35743,7 +35591,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
       <c r="W2" s="42" t="n"/>
@@ -41260,7 +41108,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
       <c r="I2" s="42" t="n"/>
@@ -43159,7 +43007,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -43170,7 +43018,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
     </row>
@@ -43347,7 +43195,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D52+F7*(1-변수!D52),"")</f>
+        <f>IFERROR(E7*변수!D51+F7*(1-변수!D51),"")</f>
         <v/>
       </c>
     </row>
@@ -43358,7 +43206,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -43382,7 +43230,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D50</f>
+        <f>변수!D49</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -43406,7 +43254,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D51</f>
+        <f>변수!D50</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -43470,7 +43318,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
     </row>
@@ -45269,7 +45117,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D59</f>
+        <f>변수!D58</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5357,35 +5357,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6071,35 +6071,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6190,35 +6190,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6325,7 +6325,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2200</v>
+        <v>2155</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2177</v>
+        <v>2168</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9760,11 +9760,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>2200</v>
+        <v>2155</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,105원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,090원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.078475197538492</v>
+        <v>0.07847519753849203</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.09303260255191068</v>
+        <v>0.09303260255191062</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5357,35 +5357,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6071,35 +6071,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6190,35 +6190,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2155</v>
+        <v>2210</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6416,7 +6416,7 @@
         <v>3020</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2290</v>
+        <v>2380</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2168</v>
+        <v>2175</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>2155</v>
+        <v>2210</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35604,7 +35604,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41121,7 +41121,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43400,7 +43400,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5357,35 +5357,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6071,35 +6071,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6190,35 +6190,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6325,7 +6325,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6416,7 +6416,7 @@
         <v>3020</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2380</v>
+        <v>2430</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2175</v>
+        <v>2179.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9760,11 +9760,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,090원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,165원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35604,7 +35604,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41121,7 +41121,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5357,35 +5357,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6071,35 +6071,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6190,35 +6190,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6325,7 +6325,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2179.3</v>
+        <v>2181.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9760,11 +9760,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,165원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,205원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35604,7 +35604,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41121,7 +41121,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43400,7 +43400,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5357,35 +5357,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6071,35 +6071,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6190,35 +6190,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6325,7 +6325,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2181.9</v>
+        <v>2189.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35604,7 +35604,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41121,7 +41121,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012160_model.xlsx
+++ b/argus/kship/models/012160_model.xlsx
@@ -4479,7 +4479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5357,35 +5357,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5476,35 +5476,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5595,35 +5595,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5714,35 +5714,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5833,35 +5833,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5952,35 +5952,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6071,35 +6071,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6190,35 +6190,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6325,7 +6325,7 @@
         <v>2120</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2190</v>
+        <v>1935</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>1284</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2020</v>
+        <v>1920</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6598,7 +6598,7 @@
         <v>2271.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2189.5</v>
+        <v>2170.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9760,11 +9760,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>2190</v>
+        <v>1935</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,205원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,165원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35604,7 +35604,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41121,7 +41121,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43400,7 +43400,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">
